--- a/files/quran.xlsx
+++ b/files/quran.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6560" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="6560"/>
   </bookViews>
   <sheets>
     <sheet name="Quran Pages" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="228">
   <si>
     <t>No Surat</t>
   </si>
@@ -1755,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F663"/>
+  <dimension ref="A1:F664"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -14942,77 +14942,76 @@
         <v>1</v>
       </c>
       <c r="D628" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E628" s="3">
         <v>589</v>
       </c>
       <c r="F628" s="3">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="629" spans="1:6">
       <c r="A629" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B629" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C629" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D629" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E629" s="3">
         <v>590</v>
       </c>
       <c r="F629" s="3">
-        <f t="shared" si="9"/>
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="630" spans="1:6">
       <c r="A630" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B630" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C630" s="3">
         <v>1</v>
       </c>
       <c r="D630" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E630" s="3">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F630" s="3">
-        <f t="shared" si="9"/>
-        <v>17</v>
+        <f>D630-C630+1</f>
+        <v>22</v>
       </c>
     </row>
     <row r="631" spans="1:6">
       <c r="A631" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B631" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C631" s="3">
         <v>1</v>
       </c>
       <c r="D631" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E631" s="3">
         <v>591</v>
       </c>
       <c r="F631" s="3">
-        <f t="shared" si="9"/>
-        <v>15</v>
+        <f>D631-C631+1</f>
+        <v>17</v>
       </c>
     </row>
     <row r="632" spans="1:6">
@@ -15023,59 +15022,59 @@
         <v>92</v>
       </c>
       <c r="C632" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D632" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E632" s="3">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F632" s="3">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f>D632-C632+1</f>
+        <v>15</v>
       </c>
     </row>
     <row r="633" spans="1:6">
       <c r="A633" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B633" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C633" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D633" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E633" s="3">
         <v>592</v>
       </c>
       <c r="F633" s="3">
-        <f t="shared" si="9"/>
-        <v>26</v>
+        <f>D633-C633+1</f>
+        <v>4</v>
       </c>
     </row>
     <row r="634" spans="1:6">
       <c r="A634" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B634" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C634" s="3">
         <v>1</v>
       </c>
       <c r="D634" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E634" s="3">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F634" s="3">
-        <f t="shared" si="9"/>
-        <v>23</v>
+        <f>D634-C634+1</f>
+        <v>26</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -15086,80 +15085,80 @@
         <v>94</v>
       </c>
       <c r="C635" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D635" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E635" s="3">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F635" s="3">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <f>D635-C635+1</f>
+        <v>23</v>
       </c>
     </row>
     <row r="636" spans="1:6">
       <c r="A636" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B636" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C636" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D636" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E636" s="3">
         <v>594</v>
       </c>
       <c r="F636" s="3">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f>D636-C636+1</f>
+        <v>7</v>
       </c>
     </row>
     <row r="637" spans="1:6">
       <c r="A637" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B637" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C637" s="3">
         <v>1</v>
       </c>
       <c r="D637" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E637" s="3">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F637" s="3">
-        <f t="shared" si="9"/>
-        <v>15</v>
+        <f>D637-C637+1</f>
+        <v>20</v>
       </c>
     </row>
     <row r="638" spans="1:6">
       <c r="A638" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B638" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C638" s="3">
         <v>1</v>
       </c>
       <c r="D638" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E638" s="3">
         <v>595</v>
       </c>
       <c r="F638" s="3">
-        <f t="shared" si="9"/>
-        <v>14</v>
+        <f>D638-C638+1</f>
+        <v>15</v>
       </c>
     </row>
     <row r="639" spans="1:6">
@@ -15170,67 +15169,67 @@
         <v>97</v>
       </c>
       <c r="C639" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D639" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E639" s="3">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F639" s="3">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <f>D639-C639+1</f>
+        <v>14</v>
       </c>
     </row>
     <row r="640" spans="1:6">
       <c r="A640" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B640" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C640" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D640" s="3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E640" s="3">
         <v>596</v>
       </c>
       <c r="F640" s="3">
-        <f t="shared" si="9"/>
-        <v>11</v>
+        <f>D640-C640+1</f>
+        <v>7</v>
       </c>
     </row>
     <row r="641" spans="1:6">
       <c r="A641" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B641" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C641" s="3">
         <v>1</v>
       </c>
       <c r="D641" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E641" s="3">
         <v>596</v>
       </c>
       <c r="F641" s="3">
-        <f t="shared" si="9"/>
-        <v>8</v>
+        <f>D641-C641+1</f>
+        <v>11</v>
       </c>
     </row>
     <row r="642" spans="1:6">
       <c r="A642" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B642" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C642" s="3">
         <v>1</v>
@@ -15239,74 +15238,74 @@
         <v>8</v>
       </c>
       <c r="E642" s="3">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F642" s="3">
-        <f t="shared" si="9"/>
+        <f>D642-C642+1</f>
         <v>8</v>
       </c>
     </row>
     <row r="643" spans="1:6">
       <c r="A643" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B643" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C643" s="3">
         <v>1</v>
       </c>
       <c r="D643" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E643" s="3">
         <v>597</v>
       </c>
       <c r="F643" s="3">
-        <f t="shared" ref="F643:F663" si="10">D643-C643+1</f>
-        <v>19</v>
+        <f>D643-C643+1</f>
+        <v>8</v>
       </c>
     </row>
     <row r="644" spans="1:6">
       <c r="A644" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B644" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C644" s="3">
         <v>1</v>
       </c>
       <c r="D644" s="3">
+        <v>19</v>
+      </c>
+      <c r="E644" s="3">
+        <v>597</v>
+      </c>
+      <c r="F644" s="3">
+        <f t="shared" ref="F644:F664" si="10">D644-C644+1</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6">
+      <c r="A645" s="1">
+        <v>97</v>
+      </c>
+      <c r="B645" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C645" s="3">
+        <v>1</v>
+      </c>
+      <c r="D645" s="3">
         <v>5</v>
       </c>
-      <c r="E644" s="3">
+      <c r="E645" s="3">
         <v>598</v>
       </c>
-      <c r="F644" s="3">
+      <c r="F645" s="3">
         <f t="shared" si="10"/>
         <v>5</v>
-      </c>
-    </row>
-    <row r="645" spans="1:6">
-      <c r="A645" s="1">
-        <v>98</v>
-      </c>
-      <c r="B645" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C645" s="3">
-        <v>1</v>
-      </c>
-      <c r="D645" s="3">
-        <v>7</v>
-      </c>
-      <c r="E645" s="3">
-        <v>598</v>
-      </c>
-      <c r="F645" s="3">
-        <f t="shared" si="10"/>
-        <v>7</v>
       </c>
     </row>
     <row r="646" spans="1:6">
@@ -15317,28 +15316,28 @@
         <v>103</v>
       </c>
       <c r="C646" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D646" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E646" s="3">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F646" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="647" spans="1:6">
       <c r="A647" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B647" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C647" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D647" s="3">
         <v>8</v>
@@ -15348,28 +15347,28 @@
       </c>
       <c r="F647" s="3">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648" spans="1:6">
       <c r="A648" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B648" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C648" s="3">
         <v>1</v>
       </c>
       <c r="D648" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E648" s="3">
         <v>599</v>
       </c>
       <c r="F648" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="649" spans="1:6">
@@ -15380,28 +15379,28 @@
         <v>105</v>
       </c>
       <c r="C649" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D649" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E649" s="3">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F649" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="650" spans="1:6">
       <c r="A650" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B650" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C650" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D650" s="3">
         <v>11</v>
@@ -15411,278 +15410,299 @@
       </c>
       <c r="F650" s="3">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="651" spans="1:6">
       <c r="A651" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B651" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C651" s="3">
         <v>1</v>
       </c>
       <c r="D651" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E651" s="3">
         <v>600</v>
       </c>
       <c r="F651" s="3">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="652" spans="1:6">
       <c r="A652" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B652" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C652" s="3">
         <v>1</v>
       </c>
       <c r="D652" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E652" s="3">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F652" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="653" spans="1:6">
       <c r="A653" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C653" s="3">
         <v>1</v>
       </c>
       <c r="D653" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E653" s="3">
         <v>601</v>
       </c>
       <c r="F653" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654" spans="1:6">
       <c r="A654" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B654" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C654" s="3">
         <v>1</v>
       </c>
       <c r="D654" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E654" s="3">
         <v>601</v>
       </c>
       <c r="F654" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="655" spans="1:6">
       <c r="A655" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B655" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C655" s="3">
         <v>1</v>
       </c>
       <c r="D655" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E655" s="3">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F655" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="656" spans="1:6">
       <c r="A656" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B656" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C656" s="3">
         <v>1</v>
       </c>
       <c r="D656" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E656" s="3">
         <v>602</v>
       </c>
       <c r="F656" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="657" spans="1:6">
       <c r="A657" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B657" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C657" s="3">
         <v>1</v>
       </c>
       <c r="D657" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E657" s="3">
         <v>602</v>
       </c>
       <c r="F657" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="658" spans="1:6">
       <c r="A658" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B658" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C658" s="3">
         <v>1</v>
       </c>
       <c r="D658" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E658" s="3">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F658" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="659" spans="1:6">
       <c r="A659" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B659" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C659" s="3">
         <v>1</v>
       </c>
       <c r="D659" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E659" s="3">
         <v>603</v>
       </c>
       <c r="F659" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="660" spans="1:6">
       <c r="A660" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B660" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C660" s="3">
         <v>1</v>
       </c>
       <c r="D660" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E660" s="3">
         <v>603</v>
       </c>
       <c r="F660" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="661" spans="1:6">
       <c r="A661" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B661" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C661" s="3">
         <v>1</v>
       </c>
       <c r="D661" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E661" s="3">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F661" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="662" spans="1:6">
       <c r="A662" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B662" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C662" s="3">
         <v>1</v>
       </c>
       <c r="D662" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E662" s="3">
         <v>604</v>
       </c>
       <c r="F662" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="663" spans="1:6">
       <c r="A663" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B663" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C663" s="3">
         <v>1</v>
       </c>
       <c r="D663" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E663" s="3">
         <v>604</v>
       </c>
       <c r="F663" s="3">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6">
+      <c r="A664" s="1">
+        <v>114</v>
+      </c>
+      <c r="B664" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C664" s="3">
+        <v>1</v>
+      </c>
+      <c r="D664" s="3">
+        <v>6</v>
+      </c>
+      <c r="E664" s="3">
+        <v>604</v>
+      </c>
+      <c r="F664" s="3">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
@@ -21971,7 +21991,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -21979,7 +21999,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="592" spans="1:2">

--- a/files/quran.xlsx
+++ b/files/quran.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6560"/>
+    <workbookView windowWidth="18350" windowHeight="6560" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Quran Pages" sheetId="1" r:id="rId1"/>
@@ -891,7 +891,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,6 +901,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E7D32"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1236,7 +1242,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1260,16 +1266,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1278,89 +1284,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1372,6 +1378,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14989,7 +14998,7 @@
         <v>590</v>
       </c>
       <c r="F630" s="3">
-        <f>D630-C630+1</f>
+        <f t="shared" ref="F630:F643" si="10">D630-C630+1</f>
         <v>22</v>
       </c>
     </row>
@@ -15010,7 +15019,7 @@
         <v>591</v>
       </c>
       <c r="F631" s="3">
-        <f>D631-C631+1</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
     </row>
@@ -15031,7 +15040,7 @@
         <v>591</v>
       </c>
       <c r="F632" s="3">
-        <f>D632-C632+1</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
     </row>
@@ -15052,7 +15061,7 @@
         <v>592</v>
       </c>
       <c r="F633" s="3">
-        <f>D633-C633+1</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -15073,7 +15082,7 @@
         <v>592</v>
       </c>
       <c r="F634" s="3">
-        <f>D634-C634+1</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
     </row>
@@ -15094,7 +15103,7 @@
         <v>593</v>
       </c>
       <c r="F635" s="3">
-        <f>D635-C635+1</f>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
     </row>
@@ -15115,7 +15124,7 @@
         <v>594</v>
       </c>
       <c r="F636" s="3">
-        <f>D636-C636+1</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -15136,7 +15145,7 @@
         <v>594</v>
       </c>
       <c r="F637" s="3">
-        <f>D637-C637+1</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
     </row>
@@ -15157,7 +15166,7 @@
         <v>595</v>
       </c>
       <c r="F638" s="3">
-        <f>D638-C638+1</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
     </row>
@@ -15178,7 +15187,7 @@
         <v>595</v>
       </c>
       <c r="F639" s="3">
-        <f>D639-C639+1</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>
@@ -15199,7 +15208,7 @@
         <v>596</v>
       </c>
       <c r="F640" s="3">
-        <f>D640-C640+1</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -15220,7 +15229,7 @@
         <v>596</v>
       </c>
       <c r="F641" s="3">
-        <f>D641-C641+1</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -15241,7 +15250,7 @@
         <v>596</v>
       </c>
       <c r="F642" s="3">
-        <f>D642-C642+1</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -15262,7 +15271,7 @@
         <v>597</v>
       </c>
       <c r="F643" s="3">
-        <f>D643-C643+1</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -15283,7 +15292,7 @@
         <v>597</v>
       </c>
       <c r="F644" s="3">
-        <f t="shared" ref="F644:F664" si="10">D644-C644+1</f>
+        <f t="shared" ref="F644:F664" si="11">D644-C644+1</f>
         <v>19</v>
       </c>
     </row>
@@ -15304,7 +15313,7 @@
         <v>598</v>
       </c>
       <c r="F645" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
     </row>
@@ -15325,7 +15334,7 @@
         <v>598</v>
       </c>
       <c r="F646" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -15346,7 +15355,7 @@
         <v>599</v>
       </c>
       <c r="F647" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -15367,7 +15376,7 @@
         <v>599</v>
       </c>
       <c r="F648" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
     </row>
@@ -15382,14 +15391,14 @@
         <v>1</v>
       </c>
       <c r="D649" s="3">
-        <v>9</v>
-      </c>
-      <c r="E649" s="3">
+        <v>5</v>
+      </c>
+      <c r="E649" s="5">
         <v>599</v>
       </c>
       <c r="F649" s="3">
-        <f t="shared" si="10"/>
-        <v>9</v>
+        <f t="shared" si="11"/>
+        <v>5</v>
       </c>
     </row>
     <row r="650" spans="1:6">
@@ -15400,7 +15409,7 @@
         <v>105</v>
       </c>
       <c r="C650" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D650" s="3">
         <v>11</v>
@@ -15409,8 +15418,8 @@
         <v>600</v>
       </c>
       <c r="F650" s="3">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f t="shared" si="11"/>
+        <v>6</v>
       </c>
     </row>
     <row r="651" spans="1:6">
@@ -15430,7 +15439,7 @@
         <v>600</v>
       </c>
       <c r="F651" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
     </row>
@@ -15451,7 +15460,7 @@
         <v>600</v>
       </c>
       <c r="F652" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
     </row>
@@ -15472,7 +15481,7 @@
         <v>601</v>
       </c>
       <c r="F653" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -15493,7 +15502,7 @@
         <v>601</v>
       </c>
       <c r="F654" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -15514,7 +15523,7 @@
         <v>601</v>
       </c>
       <c r="F655" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
     </row>
@@ -15535,7 +15544,7 @@
         <v>602</v>
       </c>
       <c r="F656" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
     </row>
@@ -15556,7 +15565,7 @@
         <v>602</v>
       </c>
       <c r="F657" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -15577,7 +15586,7 @@
         <v>602</v>
       </c>
       <c r="F658" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -15598,7 +15607,7 @@
         <v>603</v>
       </c>
       <c r="F659" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -15619,7 +15628,7 @@
         <v>603</v>
       </c>
       <c r="F660" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -15640,7 +15649,7 @@
         <v>603</v>
       </c>
       <c r="F661" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
     </row>
@@ -15661,7 +15670,7 @@
         <v>604</v>
       </c>
       <c r="F662" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
     </row>
@@ -15682,7 +15691,7 @@
         <v>604</v>
       </c>
       <c r="F663" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
     </row>
@@ -15703,7 +15712,7 @@
         <v>604</v>
       </c>
       <c r="F664" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -22071,7 +22080,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -22079,7 +22088,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="602" spans="1:2">

--- a/files/quran.xlsx
+++ b/files/quran.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6560" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="6560"/>
   </bookViews>
   <sheets>
     <sheet name="Quran Pages" sheetId="1" r:id="rId1"/>
@@ -1366,7 +1366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1375,6 +1375,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1798,7 +1801,7 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3">
@@ -1819,7 +1822,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="3">
@@ -1840,7 +1843,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3">
@@ -1861,7 +1864,7 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="3">
@@ -1882,7 +1885,7 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3">
@@ -1903,7 +1906,7 @@
       <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="3">
@@ -1924,7 +1927,7 @@
       <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3">
@@ -1945,7 +1948,7 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="3">
@@ -1966,7 +1969,7 @@
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3">
@@ -1987,7 +1990,7 @@
       <c r="A11" s="1">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="3">
@@ -2008,7 +2011,7 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="3">
@@ -2029,7 +2032,7 @@
       <c r="A13" s="1">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3">
@@ -2050,7 +2053,7 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="3">
@@ -2071,7 +2074,7 @@
       <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="3">
@@ -2092,7 +2095,7 @@
       <c r="A16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="3">
@@ -2113,7 +2116,7 @@
       <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="3">
@@ -2134,7 +2137,7 @@
       <c r="A18" s="1">
         <v>2</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="3">
@@ -2155,7 +2158,7 @@
       <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="3">
@@ -2176,7 +2179,7 @@
       <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="3">
@@ -2197,7 +2200,7 @@
       <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="3">
@@ -2218,7 +2221,7 @@
       <c r="A22" s="1">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="3">
@@ -2239,7 +2242,7 @@
       <c r="A23" s="1">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="3">
@@ -2260,7 +2263,7 @@
       <c r="A24" s="1">
         <v>2</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3">
@@ -2281,7 +2284,7 @@
       <c r="A25" s="1">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="3">
@@ -2302,7 +2305,7 @@
       <c r="A26" s="1">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="3">
@@ -2323,7 +2326,7 @@
       <c r="A27" s="1">
         <v>2</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="3">
@@ -2344,7 +2347,7 @@
       <c r="A28" s="1">
         <v>2</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="3">
@@ -2365,7 +2368,7 @@
       <c r="A29" s="1">
         <v>2</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="3">
@@ -2386,7 +2389,7 @@
       <c r="A30" s="1">
         <v>2</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="3">
@@ -2407,7 +2410,7 @@
       <c r="A31" s="1">
         <v>2</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="3">
@@ -2428,7 +2431,7 @@
       <c r="A32" s="1">
         <v>2</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="3">
@@ -2449,7 +2452,7 @@
       <c r="A33" s="1">
         <v>2</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="3">
@@ -2470,7 +2473,7 @@
       <c r="A34" s="1">
         <v>2</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="3">
@@ -2491,7 +2494,7 @@
       <c r="A35" s="1">
         <v>2</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="3">
@@ -2512,7 +2515,7 @@
       <c r="A36" s="1">
         <v>2</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="3">
@@ -2533,7 +2536,7 @@
       <c r="A37" s="1">
         <v>2</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="3">
@@ -2554,7 +2557,7 @@
       <c r="A38" s="1">
         <v>2</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="3">
@@ -2575,7 +2578,7 @@
       <c r="A39" s="1">
         <v>2</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="3">
@@ -2596,7 +2599,7 @@
       <c r="A40" s="1">
         <v>2</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="3">
@@ -2617,7 +2620,7 @@
       <c r="A41" s="1">
         <v>2</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="3">
@@ -2638,7 +2641,7 @@
       <c r="A42" s="1">
         <v>2</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="3">
@@ -2659,7 +2662,7 @@
       <c r="A43" s="1">
         <v>2</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="3">
@@ -2680,7 +2683,7 @@
       <c r="A44" s="1">
         <v>2</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="3">
@@ -2701,7 +2704,7 @@
       <c r="A45" s="1">
         <v>2</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="3">
@@ -2722,7 +2725,7 @@
       <c r="A46" s="1">
         <v>2</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="3">
@@ -2743,7 +2746,7 @@
       <c r="A47" s="1">
         <v>2</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="3">
@@ -2764,7 +2767,7 @@
       <c r="A48" s="1">
         <v>2</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="3">
@@ -2785,7 +2788,7 @@
       <c r="A49" s="1">
         <v>2</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="3">
@@ -2806,7 +2809,7 @@
       <c r="A50" s="1">
         <v>2</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="3">
@@ -2827,7 +2830,7 @@
       <c r="A51" s="1">
         <v>3</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="3">
@@ -2848,7 +2851,7 @@
       <c r="A52" s="1">
         <v>3</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="3">
@@ -2869,7 +2872,7 @@
       <c r="A53" s="1">
         <v>3</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="3">
@@ -2890,7 +2893,7 @@
       <c r="A54" s="1">
         <v>3</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="3">
@@ -2911,7 +2914,7 @@
       <c r="A55" s="1">
         <v>3</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="3">
@@ -2932,7 +2935,7 @@
       <c r="A56" s="1">
         <v>3</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="3">
@@ -2953,7 +2956,7 @@
       <c r="A57" s="1">
         <v>3</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="3">
@@ -2974,7 +2977,7 @@
       <c r="A58" s="1">
         <v>3</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="3">
@@ -2995,7 +2998,7 @@
       <c r="A59" s="1">
         <v>3</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="3">
@@ -3016,7 +3019,7 @@
       <c r="A60" s="1">
         <v>3</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="3">
@@ -3037,7 +3040,7 @@
       <c r="A61" s="1">
         <v>3</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="3">
@@ -3058,7 +3061,7 @@
       <c r="A62" s="1">
         <v>3</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="3">
@@ -3079,7 +3082,7 @@
       <c r="A63" s="1">
         <v>3</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="3">
@@ -3100,7 +3103,7 @@
       <c r="A64" s="1">
         <v>3</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="3">
@@ -3121,7 +3124,7 @@
       <c r="A65" s="1">
         <v>3</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="3">
@@ -3142,7 +3145,7 @@
       <c r="A66" s="1">
         <v>3</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="3">
@@ -3163,7 +3166,7 @@
       <c r="A67" s="1">
         <v>3</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="3">
@@ -3184,7 +3187,7 @@
       <c r="A68" s="1">
         <v>3</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="3">
@@ -3205,7 +3208,7 @@
       <c r="A69" s="1">
         <v>3</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="3">
@@ -3226,7 +3229,7 @@
       <c r="A70" s="1">
         <v>3</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="3">
@@ -3247,7 +3250,7 @@
       <c r="A71" s="1">
         <v>3</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="3">
@@ -3268,7 +3271,7 @@
       <c r="A72" s="1">
         <v>3</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="3">
@@ -3289,7 +3292,7 @@
       <c r="A73" s="1">
         <v>3</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="3">
@@ -3310,7 +3313,7 @@
       <c r="A74" s="1">
         <v>3</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="3">
@@ -3331,7 +3334,7 @@
       <c r="A75" s="1">
         <v>3</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="3">
@@ -3352,7 +3355,7 @@
       <c r="A76" s="1">
         <v>3</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="3">
@@ -3373,7 +3376,7 @@
       <c r="A77" s="1">
         <v>3</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="3">
@@ -3394,7 +3397,7 @@
       <c r="A78" s="1">
         <v>4</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C78" s="3">
@@ -3415,7 +3418,7 @@
       <c r="A79" s="1">
         <v>4</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C79" s="3">
@@ -3436,7 +3439,7 @@
       <c r="A80" s="1">
         <v>4</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C80" s="3">
@@ -3457,7 +3460,7 @@
       <c r="A81" s="1">
         <v>4</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C81" s="3">
@@ -3478,7 +3481,7 @@
       <c r="A82" s="1">
         <v>4</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C82" s="3">
@@ -3499,7 +3502,7 @@
       <c r="A83" s="1">
         <v>4</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C83" s="3">
@@ -3520,7 +3523,7 @@
       <c r="A84" s="1">
         <v>4</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C84" s="3">
@@ -3541,7 +3544,7 @@
       <c r="A85" s="1">
         <v>4</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C85" s="3">
@@ -3562,7 +3565,7 @@
       <c r="A86" s="1">
         <v>4</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C86" s="3">
@@ -3583,7 +3586,7 @@
       <c r="A87" s="1">
         <v>4</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C87" s="3">
@@ -3604,7 +3607,7 @@
       <c r="A88" s="1">
         <v>4</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C88" s="3">
@@ -3625,7 +3628,7 @@
       <c r="A89" s="1">
         <v>4</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C89" s="3">
@@ -3646,7 +3649,7 @@
       <c r="A90" s="1">
         <v>4</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C90" s="3">
@@ -3667,7 +3670,7 @@
       <c r="A91" s="1">
         <v>4</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C91" s="3">
@@ -3688,7 +3691,7 @@
       <c r="A92" s="1">
         <v>4</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C92" s="3">
@@ -3709,7 +3712,7 @@
       <c r="A93" s="1">
         <v>4</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="3">
@@ -3730,7 +3733,7 @@
       <c r="A94" s="1">
         <v>4</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C94" s="3">
@@ -3751,7 +3754,7 @@
       <c r="A95" s="1">
         <v>4</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="3">
@@ -3772,7 +3775,7 @@
       <c r="A96" s="1">
         <v>4</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="3">
@@ -3793,7 +3796,7 @@
       <c r="A97" s="1">
         <v>4</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C97" s="3">
@@ -3814,7 +3817,7 @@
       <c r="A98" s="1">
         <v>4</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="3">
@@ -3835,7 +3838,7 @@
       <c r="A99" s="1">
         <v>4</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C99" s="3">
@@ -3856,7 +3859,7 @@
       <c r="A100" s="1">
         <v>4</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C100" s="3">
@@ -3877,7 +3880,7 @@
       <c r="A101" s="1">
         <v>4</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C101" s="3">
@@ -3898,7 +3901,7 @@
       <c r="A102" s="1">
         <v>4</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C102" s="3">
@@ -3919,7 +3922,7 @@
       <c r="A103" s="1">
         <v>4</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C103" s="3">
@@ -3940,7 +3943,7 @@
       <c r="A104" s="1">
         <v>4</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="3">
@@ -3961,7 +3964,7 @@
       <c r="A105" s="1">
         <v>4</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C105" s="3">
@@ -3982,7 +3985,7 @@
       <c r="A106" s="1">
         <v>4</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C106" s="3">
@@ -4003,7 +4006,7 @@
       <c r="A107" s="1">
         <v>4</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="3">
@@ -4024,7 +4027,7 @@
       <c r="A108" s="1">
         <v>5</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="3">
@@ -4045,7 +4048,7 @@
       <c r="A109" s="1">
         <v>5</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="3">
@@ -4066,7 +4069,7 @@
       <c r="A110" s="1">
         <v>5</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C110" s="3">
@@ -4087,7 +4090,7 @@
       <c r="A111" s="1">
         <v>5</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="3">
@@ -4108,7 +4111,7 @@
       <c r="A112" s="1">
         <v>5</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="3">
@@ -4129,7 +4132,7 @@
       <c r="A113" s="1">
         <v>5</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C113" s="3">
@@ -4150,7 +4153,7 @@
       <c r="A114" s="1">
         <v>5</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="3">
@@ -4171,7 +4174,7 @@
       <c r="A115" s="1">
         <v>5</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C115" s="3">
@@ -4192,7 +4195,7 @@
       <c r="A116" s="1">
         <v>5</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="3">
@@ -4213,7 +4216,7 @@
       <c r="A117" s="1">
         <v>5</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C117" s="3">
@@ -4234,7 +4237,7 @@
       <c r="A118" s="1">
         <v>5</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C118" s="3">
@@ -4255,7 +4258,7 @@
       <c r="A119" s="1">
         <v>5</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C119" s="3">
@@ -4276,7 +4279,7 @@
       <c r="A120" s="1">
         <v>5</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="3">
@@ -4297,7 +4300,7 @@
       <c r="A121" s="1">
         <v>5</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="3">
@@ -4318,40 +4321,40 @@
       <c r="A122" s="1">
         <v>5</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="3">
         <v>71</v>
       </c>
-      <c r="D122" s="3">
-        <v>76</v>
+      <c r="D122" s="6">
+        <v>77</v>
       </c>
       <c r="E122" s="3">
         <v>120</v>
       </c>
       <c r="F122" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>5</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C123" s="3">
-        <v>77</v>
-      </c>
-      <c r="D123" s="3">
-        <v>82</v>
+      <c r="C123" s="6">
+        <v>78</v>
+      </c>
+      <c r="D123" s="6">
+        <v>83</v>
       </c>
       <c r="E123" s="3">
         <v>121</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -4360,19 +4363,19 @@
       <c r="A124" s="1">
         <v>5</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C124" s="3">
-        <v>83</v>
-      </c>
-      <c r="D124" s="3">
-        <v>89</v>
+      <c r="C124" s="6">
+        <v>84</v>
+      </c>
+      <c r="D124" s="6">
+        <v>90</v>
       </c>
       <c r="E124" s="3">
         <v>122</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="6">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -4381,11 +4384,11 @@
       <c r="A125" s="1">
         <v>5</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D125" s="3">
         <v>95</v>
@@ -4395,14 +4398,14 @@
       </c>
       <c r="F125" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>5</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="3">
@@ -4423,7 +4426,7 @@
       <c r="A127" s="1">
         <v>5</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C127" s="3">
@@ -4444,7 +4447,7 @@
       <c r="A128" s="1">
         <v>5</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="3">
@@ -4465,7 +4468,7 @@
       <c r="A129" s="1">
         <v>5</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="3">
@@ -4486,7 +4489,7 @@
       <c r="A130" s="1">
         <v>6</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C130" s="3">
@@ -4507,7 +4510,7 @@
       <c r="A131" s="1">
         <v>6</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C131" s="3">
@@ -4528,7 +4531,7 @@
       <c r="A132" s="1">
         <v>6</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C132" s="3">
@@ -4549,7 +4552,7 @@
       <c r="A133" s="1">
         <v>6</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C133" s="3">
@@ -4570,7 +4573,7 @@
       <c r="A134" s="1">
         <v>6</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C134" s="3">
@@ -4591,7 +4594,7 @@
       <c r="A135" s="1">
         <v>6</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="3">
@@ -4612,7 +4615,7 @@
       <c r="A136" s="1">
         <v>6</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C136" s="3">
@@ -4633,7 +4636,7 @@
       <c r="A137" s="1">
         <v>6</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C137" s="3">
@@ -4654,7 +4657,7 @@
       <c r="A138" s="1">
         <v>6</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C138" s="3">
@@ -4675,7 +4678,7 @@
       <c r="A139" s="1">
         <v>6</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C139" s="3">
@@ -4696,7 +4699,7 @@
       <c r="A140" s="1">
         <v>6</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C140" s="3">
@@ -4717,7 +4720,7 @@
       <c r="A141" s="1">
         <v>6</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C141" s="3">
@@ -4738,7 +4741,7 @@
       <c r="A142" s="1">
         <v>6</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C142" s="3">
@@ -4759,7 +4762,7 @@
       <c r="A143" s="1">
         <v>6</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C143" s="3">
@@ -4780,7 +4783,7 @@
       <c r="A144" s="1">
         <v>6</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C144" s="3">
@@ -4801,7 +4804,7 @@
       <c r="A145" s="1">
         <v>6</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C145" s="3">
@@ -4822,32 +4825,32 @@
       <c r="A146" s="1">
         <v>6</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C146" s="3">
         <v>125</v>
       </c>
-      <c r="D146" s="3">
-        <v>131</v>
+      <c r="D146" s="6">
+        <v>130</v>
       </c>
       <c r="E146" s="3">
         <v>144</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="6">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>6</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C147" s="3">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D147" s="3">
         <v>137</v>
@@ -4855,16 +4858,16 @@
       <c r="E147" s="3">
         <v>145</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="6">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>6</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C148" s="3">
@@ -4885,7 +4888,7 @@
       <c r="A149" s="1">
         <v>6</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C149" s="3">
@@ -4906,7 +4909,7 @@
       <c r="A150" s="1">
         <v>6</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C150" s="3">
@@ -4927,7 +4930,7 @@
       <c r="A151" s="1">
         <v>6</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C151" s="3">
@@ -4948,7 +4951,7 @@
       <c r="A152" s="1">
         <v>6</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C152" s="3">
@@ -4969,7 +4972,7 @@
       <c r="A153" s="1">
         <v>7</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C153" s="3">
@@ -4990,7 +4993,7 @@
       <c r="A154" s="1">
         <v>7</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C154" s="3">
@@ -5011,7 +5014,7 @@
       <c r="A155" s="1">
         <v>7</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C155" s="3">
@@ -5032,7 +5035,7 @@
       <c r="A156" s="1">
         <v>7</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C156" s="3">
@@ -5053,7 +5056,7 @@
       <c r="A157" s="1">
         <v>7</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C157" s="3">
@@ -5074,7 +5077,7 @@
       <c r="A158" s="1">
         <v>7</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C158" s="3">
@@ -5095,7 +5098,7 @@
       <c r="A159" s="1">
         <v>7</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C159" s="3">
@@ -5116,7 +5119,7 @@
       <c r="A160" s="1">
         <v>7</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C160" s="3">
@@ -5137,7 +5140,7 @@
       <c r="A161" s="1">
         <v>7</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C161" s="3">
@@ -5158,7 +5161,7 @@
       <c r="A162" s="1">
         <v>7</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C162" s="3">
@@ -5179,7 +5182,7 @@
       <c r="A163" s="1">
         <v>7</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C163" s="3">
@@ -5200,7 +5203,7 @@
       <c r="A164" s="1">
         <v>7</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C164" s="3">
@@ -5221,7 +5224,7 @@
       <c r="A165" s="1">
         <v>7</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C165" s="3">
@@ -5242,7 +5245,7 @@
       <c r="A166" s="1">
         <v>7</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C166" s="3">
@@ -5263,7 +5266,7 @@
       <c r="A167" s="1">
         <v>7</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C167" s="3">
@@ -5284,7 +5287,7 @@
       <c r="A168" s="1">
         <v>7</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C168" s="3">
@@ -5305,7 +5308,7 @@
       <c r="A169" s="1">
         <v>7</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C169" s="3">
@@ -5326,7 +5329,7 @@
       <c r="A170" s="1">
         <v>7</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C170" s="3">
@@ -5347,7 +5350,7 @@
       <c r="A171" s="1">
         <v>7</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C171" s="3">
@@ -5368,7 +5371,7 @@
       <c r="A172" s="1">
         <v>7</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="3">
@@ -5389,7 +5392,7 @@
       <c r="A173" s="1">
         <v>7</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="3">
@@ -5410,7 +5413,7 @@
       <c r="A174" s="1">
         <v>7</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="3">
@@ -5431,7 +5434,7 @@
       <c r="A175" s="1">
         <v>7</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="3">
@@ -5452,7 +5455,7 @@
       <c r="A176" s="1">
         <v>7</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="3">
@@ -5473,7 +5476,7 @@
       <c r="A177" s="1">
         <v>7</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="3">
@@ -5494,7 +5497,7 @@
       <c r="A178" s="1">
         <v>7</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="3">
@@ -5515,7 +5518,7 @@
       <c r="A179" s="1">
         <v>8</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C179" s="3">
@@ -5536,7 +5539,7 @@
       <c r="A180" s="1">
         <v>8</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C180" s="3">
@@ -5557,7 +5560,7 @@
       <c r="A181" s="1">
         <v>8</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C181" s="3">
@@ -5578,7 +5581,7 @@
       <c r="A182" s="1">
         <v>8</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C182" s="3">
@@ -5599,7 +5602,7 @@
       <c r="A183" s="1">
         <v>8</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="3">
@@ -5620,7 +5623,7 @@
       <c r="A184" s="1">
         <v>8</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C184" s="3">
@@ -5641,7 +5644,7 @@
       <c r="A185" s="1">
         <v>8</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C185" s="3">
@@ -5662,7 +5665,7 @@
       <c r="A186" s="1">
         <v>8</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C186" s="3">
@@ -5683,7 +5686,7 @@
       <c r="A187" s="1">
         <v>8</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C187" s="3">
@@ -5704,7 +5707,7 @@
       <c r="A188" s="1">
         <v>8</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C188" s="3">
@@ -5725,7 +5728,7 @@
       <c r="A189" s="1">
         <v>9</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C189" s="3">
@@ -5746,7 +5749,7 @@
       <c r="A190" s="1">
         <v>9</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C190" s="3">
@@ -5767,7 +5770,7 @@
       <c r="A191" s="1">
         <v>9</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C191" s="3">
@@ -5788,7 +5791,7 @@
       <c r="A192" s="1">
         <v>9</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C192" s="3">
@@ -5809,7 +5812,7 @@
       <c r="A193" s="1">
         <v>9</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C193" s="3">
@@ -5830,7 +5833,7 @@
       <c r="A194" s="1">
         <v>9</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C194" s="3">
@@ -5851,7 +5854,7 @@
       <c r="A195" s="1">
         <v>9</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C195" s="3">
@@ -5872,7 +5875,7 @@
       <c r="A196" s="1">
         <v>9</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C196" s="3">
@@ -5893,7 +5896,7 @@
       <c r="A197" s="1">
         <v>9</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C197" s="3">
@@ -5914,7 +5917,7 @@
       <c r="A198" s="1">
         <v>9</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C198" s="3">
@@ -5935,7 +5938,7 @@
       <c r="A199" s="1">
         <v>9</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C199" s="3">
@@ -5956,7 +5959,7 @@
       <c r="A200" s="1">
         <v>9</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C200" s="3">
@@ -5977,7 +5980,7 @@
       <c r="A201" s="1">
         <v>9</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C201" s="3">
@@ -5998,7 +6001,7 @@
       <c r="A202" s="1">
         <v>9</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C202" s="3">
@@ -6019,7 +6022,7 @@
       <c r="A203" s="1">
         <v>9</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C203" s="3">
@@ -6040,7 +6043,7 @@
       <c r="A204" s="1">
         <v>9</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C204" s="3">
@@ -6061,7 +6064,7 @@
       <c r="A205" s="1">
         <v>9</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C205" s="3">
@@ -6082,7 +6085,7 @@
       <c r="A206" s="1">
         <v>9</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C206" s="3">
@@ -6103,7 +6106,7 @@
       <c r="A207" s="1">
         <v>9</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C207" s="3">
@@ -6124,7 +6127,7 @@
       <c r="A208" s="1">
         <v>9</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C208" s="3">
@@ -6145,7 +6148,7 @@
       <c r="A209" s="1">
         <v>9</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C209" s="3">
@@ -6166,7 +6169,7 @@
       <c r="A210" s="1">
         <v>10</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C210" s="3">
@@ -6187,7 +6190,7 @@
       <c r="A211" s="1">
         <v>10</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C211" s="3">
@@ -6208,7 +6211,7 @@
       <c r="A212" s="1">
         <v>10</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C212" s="3">
@@ -6229,7 +6232,7 @@
       <c r="A213" s="1">
         <v>10</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C213" s="3">
@@ -6250,7 +6253,7 @@
       <c r="A214" s="1">
         <v>10</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="3">
@@ -6271,7 +6274,7 @@
       <c r="A215" s="1">
         <v>10</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C215" s="3">
@@ -6292,7 +6295,7 @@
       <c r="A216" s="1">
         <v>10</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C216" s="3">
@@ -6313,7 +6316,7 @@
       <c r="A217" s="1">
         <v>10</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C217" s="3">
@@ -6334,7 +6337,7 @@
       <c r="A218" s="1">
         <v>10</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C218" s="3">
@@ -6355,7 +6358,7 @@
       <c r="A219" s="1">
         <v>10</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C219" s="3">
@@ -6376,7 +6379,7 @@
       <c r="A220" s="1">
         <v>10</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C220" s="3">
@@ -6397,7 +6400,7 @@
       <c r="A221" s="1">
         <v>10</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C221" s="3">
@@ -6418,7 +6421,7 @@
       <c r="A222" s="1">
         <v>10</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C222" s="3">
@@ -6439,7 +6442,7 @@
       <c r="A223" s="1">
         <v>10</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C223" s="3">
@@ -6460,7 +6463,7 @@
       <c r="A224" s="1">
         <v>11</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="B224" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C224" s="3">
@@ -6481,7 +6484,7 @@
       <c r="A225" s="1">
         <v>11</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C225" s="3">
@@ -6502,7 +6505,7 @@
       <c r="A226" s="1">
         <v>11</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C226" s="3">
@@ -6523,7 +6526,7 @@
       <c r="A227" s="1">
         <v>11</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B227" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C227" s="3">
@@ -6544,7 +6547,7 @@
       <c r="A228" s="1">
         <v>11</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C228" s="3">
@@ -6565,7 +6568,7 @@
       <c r="A229" s="1">
         <v>11</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C229" s="3">
@@ -6586,7 +6589,7 @@
       <c r="A230" s="1">
         <v>11</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C230" s="3">
@@ -6607,7 +6610,7 @@
       <c r="A231" s="1">
         <v>11</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B231" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C231" s="3">
@@ -6628,7 +6631,7 @@
       <c r="A232" s="1">
         <v>11</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C232" s="3">
@@ -6649,7 +6652,7 @@
       <c r="A233" s="1">
         <v>11</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C233" s="3">
@@ -6670,7 +6673,7 @@
       <c r="A234" s="1">
         <v>11</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C234" s="3">
@@ -6691,7 +6694,7 @@
       <c r="A235" s="1">
         <v>11</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C235" s="3">
@@ -6712,7 +6715,7 @@
       <c r="A236" s="1">
         <v>11</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C236" s="3">
@@ -6733,7 +6736,7 @@
       <c r="A237" s="1">
         <v>11</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C237" s="3">
@@ -6754,7 +6757,7 @@
       <c r="A238" s="1">
         <v>11</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C238" s="3">
@@ -6775,7 +6778,7 @@
       <c r="A239" s="1">
         <v>12</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C239" s="3">
@@ -6796,7 +6799,7 @@
       <c r="A240" s="1">
         <v>12</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C240" s="3">
@@ -6817,7 +6820,7 @@
       <c r="A241" s="1">
         <v>12</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C241" s="3">
@@ -6838,7 +6841,7 @@
       <c r="A242" s="1">
         <v>12</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C242" s="3">
@@ -6859,7 +6862,7 @@
       <c r="A243" s="1">
         <v>12</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B243" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C243" s="3">
@@ -6880,7 +6883,7 @@
       <c r="A244" s="1">
         <v>12</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C244" s="3">
@@ -6901,7 +6904,7 @@
       <c r="A245" s="1">
         <v>12</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C245" s="3">
@@ -6922,7 +6925,7 @@
       <c r="A246" s="1">
         <v>12</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C246" s="3">
@@ -6943,7 +6946,7 @@
       <c r="A247" s="1">
         <v>12</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B247" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C247" s="3">
@@ -6964,7 +6967,7 @@
       <c r="A248" s="1">
         <v>12</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C248" s="3">
@@ -6985,7 +6988,7 @@
       <c r="A249" s="1">
         <v>12</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C249" s="3">
@@ -7006,7 +7009,7 @@
       <c r="A250" s="1">
         <v>12</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C250" s="3">
@@ -7027,7 +7030,7 @@
       <c r="A251" s="1">
         <v>12</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C251" s="3">
@@ -7048,7 +7051,7 @@
       <c r="A252" s="1">
         <v>12</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C252" s="3">
@@ -7069,7 +7072,7 @@
       <c r="A253" s="1">
         <v>13</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B253" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C253" s="3">
@@ -7090,7 +7093,7 @@
       <c r="A254" s="1">
         <v>13</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C254" s="3">
@@ -7111,7 +7114,7 @@
       <c r="A255" s="1">
         <v>13</v>
       </c>
-      <c r="B255" s="4" t="s">
+      <c r="B255" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C255" s="3">
@@ -7132,7 +7135,7 @@
       <c r="A256" s="1">
         <v>13</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C256" s="3">
@@ -7153,7 +7156,7 @@
       <c r="A257" s="1">
         <v>13</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C257" s="3">
@@ -7174,7 +7177,7 @@
       <c r="A258" s="1">
         <v>13</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B258" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C258" s="3">
@@ -7195,7 +7198,7 @@
       <c r="A259" s="1">
         <v>13</v>
       </c>
-      <c r="B259" s="4" t="s">
+      <c r="B259" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C259" s="3">
@@ -7216,7 +7219,7 @@
       <c r="A260" s="1">
         <v>14</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C260" s="3">
@@ -7237,7 +7240,7 @@
       <c r="A261" s="1">
         <v>14</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B261" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C261" s="3">
@@ -7258,7 +7261,7 @@
       <c r="A262" s="1">
         <v>14</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="B262" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C262" s="3">
@@ -7279,7 +7282,7 @@
       <c r="A263" s="1">
         <v>14</v>
       </c>
-      <c r="B263" s="4" t="s">
+      <c r="B263" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C263" s="3">
@@ -7300,7 +7303,7 @@
       <c r="A264" s="1">
         <v>14</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C264" s="3">
@@ -7321,7 +7324,7 @@
       <c r="A265" s="1">
         <v>14</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B265" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C265" s="3">
@@ -7342,7 +7345,7 @@
       <c r="A266" s="1">
         <v>14</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C266" s="3">
@@ -7363,7 +7366,7 @@
       <c r="A267" s="1">
         <v>15</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="B267" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C267" s="3">
@@ -7384,7 +7387,7 @@
       <c r="A268" s="1">
         <v>15</v>
       </c>
-      <c r="B268" s="4" t="s">
+      <c r="B268" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C268" s="3">
@@ -7405,7 +7408,7 @@
       <c r="A269" s="1">
         <v>15</v>
       </c>
-      <c r="B269" s="4" t="s">
+      <c r="B269" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C269" s="3">
@@ -7426,7 +7429,7 @@
       <c r="A270" s="1">
         <v>15</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C270" s="3">
@@ -7447,7 +7450,7 @@
       <c r="A271" s="1">
         <v>15</v>
       </c>
-      <c r="B271" s="4" t="s">
+      <c r="B271" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C271" s="3">
@@ -7468,7 +7471,7 @@
       <c r="A272" s="1">
         <v>15</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C272" s="3">
@@ -7489,7 +7492,7 @@
       <c r="A273" s="1">
         <v>16</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C273" s="3">
@@ -7510,7 +7513,7 @@
       <c r="A274" s="1">
         <v>16</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C274" s="3">
@@ -7531,7 +7534,7 @@
       <c r="A275" s="1">
         <v>16</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C275" s="3">
@@ -7552,7 +7555,7 @@
       <c r="A276" s="1">
         <v>16</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C276" s="3">
@@ -7573,7 +7576,7 @@
       <c r="A277" s="1">
         <v>16</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C277" s="3">
@@ -7594,7 +7597,7 @@
       <c r="A278" s="1">
         <v>16</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C278" s="3">
@@ -7615,7 +7618,7 @@
       <c r="A279" s="1">
         <v>16</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C279" s="3">
@@ -7636,7 +7639,7 @@
       <c r="A280" s="1">
         <v>16</v>
       </c>
-      <c r="B280" s="4" t="s">
+      <c r="B280" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C280" s="3">
@@ -7657,7 +7660,7 @@
       <c r="A281" s="1">
         <v>16</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C281" s="3">
@@ -7678,7 +7681,7 @@
       <c r="A282" s="1">
         <v>16</v>
       </c>
-      <c r="B282" s="4" t="s">
+      <c r="B282" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C282" s="3">
@@ -7699,7 +7702,7 @@
       <c r="A283" s="1">
         <v>16</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C283" s="3">
@@ -7720,7 +7723,7 @@
       <c r="A284" s="1">
         <v>16</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B284" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C284" s="3">
@@ -7741,7 +7744,7 @@
       <c r="A285" s="1">
         <v>16</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C285" s="3">
@@ -7762,7 +7765,7 @@
       <c r="A286" s="1">
         <v>16</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B286" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C286" s="3">
@@ -7783,7 +7786,7 @@
       <c r="A287" s="1">
         <v>16</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C287" s="3">
@@ -7804,7 +7807,7 @@
       <c r="A288" s="1">
         <v>17</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B288" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C288" s="3">
@@ -7825,7 +7828,7 @@
       <c r="A289" s="1">
         <v>17</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C289" s="3">
@@ -7846,7 +7849,7 @@
       <c r="A290" s="1">
         <v>17</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C290" s="3">
@@ -7867,7 +7870,7 @@
       <c r="A291" s="1">
         <v>17</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B291" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C291" s="3">
@@ -7888,7 +7891,7 @@
       <c r="A292" s="1">
         <v>17</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B292" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C292" s="3">
@@ -7909,7 +7912,7 @@
       <c r="A293" s="1">
         <v>17</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B293" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C293" s="3">
@@ -7930,7 +7933,7 @@
       <c r="A294" s="1">
         <v>17</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C294" s="3">
@@ -7951,7 +7954,7 @@
       <c r="A295" s="1">
         <v>17</v>
       </c>
-      <c r="B295" s="4" t="s">
+      <c r="B295" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C295" s="3">
@@ -7972,7 +7975,7 @@
       <c r="A296" s="1">
         <v>17</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C296" s="3">
@@ -7993,7 +7996,7 @@
       <c r="A297" s="1">
         <v>17</v>
       </c>
-      <c r="B297" s="4" t="s">
+      <c r="B297" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C297" s="3">
@@ -8014,7 +8017,7 @@
       <c r="A298" s="1">
         <v>17</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C298" s="3">
@@ -8035,7 +8038,7 @@
       <c r="A299" s="1">
         <v>17</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B299" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C299" s="3">
@@ -8056,7 +8059,7 @@
       <c r="A300" s="1">
         <v>18</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C300" s="3">
@@ -8077,7 +8080,7 @@
       <c r="A301" s="1">
         <v>18</v>
       </c>
-      <c r="B301" s="4" t="s">
+      <c r="B301" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C301" s="3">
@@ -8098,7 +8101,7 @@
       <c r="A302" s="1">
         <v>18</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C302" s="3">
@@ -8119,7 +8122,7 @@
       <c r="A303" s="1">
         <v>18</v>
       </c>
-      <c r="B303" s="4" t="s">
+      <c r="B303" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C303" s="3">
@@ -8140,7 +8143,7 @@
       <c r="A304" s="1">
         <v>18</v>
       </c>
-      <c r="B304" s="4" t="s">
+      <c r="B304" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C304" s="3">
@@ -8161,7 +8164,7 @@
       <c r="A305" s="1">
         <v>18</v>
       </c>
-      <c r="B305" s="4" t="s">
+      <c r="B305" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C305" s="3">
@@ -8182,7 +8185,7 @@
       <c r="A306" s="1">
         <v>18</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="B306" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C306" s="3">
@@ -8203,7 +8206,7 @@
       <c r="A307" s="1">
         <v>18</v>
       </c>
-      <c r="B307" s="4" t="s">
+      <c r="B307" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C307" s="3">
@@ -8224,7 +8227,7 @@
       <c r="A308" s="1">
         <v>18</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B308" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C308" s="3">
@@ -8245,7 +8248,7 @@
       <c r="A309" s="1">
         <v>18</v>
       </c>
-      <c r="B309" s="4" t="s">
+      <c r="B309" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C309" s="3">
@@ -8266,7 +8269,7 @@
       <c r="A310" s="1">
         <v>18</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C310" s="3">
@@ -8287,7 +8290,7 @@
       <c r="A311" s="1">
         <v>18</v>
       </c>
-      <c r="B311" s="4" t="s">
+      <c r="B311" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C311" s="3">
@@ -8308,7 +8311,7 @@
       <c r="A312" s="1">
         <v>19</v>
       </c>
-      <c r="B312" s="4" t="s">
+      <c r="B312" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C312" s="3">
@@ -8329,7 +8332,7 @@
       <c r="A313" s="1">
         <v>19</v>
       </c>
-      <c r="B313" s="4" t="s">
+      <c r="B313" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C313" s="3">
@@ -8350,7 +8353,7 @@
       <c r="A314" s="1">
         <v>19</v>
       </c>
-      <c r="B314" s="4" t="s">
+      <c r="B314" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C314" s="3">
@@ -8371,7 +8374,7 @@
       <c r="A315" s="1">
         <v>19</v>
       </c>
-      <c r="B315" s="4" t="s">
+      <c r="B315" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C315" s="3">
@@ -8392,7 +8395,7 @@
       <c r="A316" s="1">
         <v>19</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="B316" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C316" s="3">
@@ -8413,7 +8416,7 @@
       <c r="A317" s="1">
         <v>19</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B317" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C317" s="3">
@@ -8434,7 +8437,7 @@
       <c r="A318" s="1">
         <v>19</v>
       </c>
-      <c r="B318" s="4" t="s">
+      <c r="B318" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C318" s="3">
@@ -8455,7 +8458,7 @@
       <c r="A319" s="1">
         <v>19</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="B319" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C319" s="3">
@@ -8476,7 +8479,7 @@
       <c r="A320" s="1">
         <v>20</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="B320" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C320" s="3">
@@ -8497,7 +8500,7 @@
       <c r="A321" s="1">
         <v>20</v>
       </c>
-      <c r="B321" s="4" t="s">
+      <c r="B321" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C321" s="3">
@@ -8518,7 +8521,7 @@
       <c r="A322" s="1">
         <v>20</v>
       </c>
-      <c r="B322" s="4" t="s">
+      <c r="B322" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C322" s="3">
@@ -8539,7 +8542,7 @@
       <c r="A323" s="1">
         <v>20</v>
       </c>
-      <c r="B323" s="4" t="s">
+      <c r="B323" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C323" s="3">
@@ -8560,7 +8563,7 @@
       <c r="A324" s="1">
         <v>20</v>
       </c>
-      <c r="B324" s="4" t="s">
+      <c r="B324" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C324" s="3">
@@ -8581,7 +8584,7 @@
       <c r="A325" s="1">
         <v>20</v>
       </c>
-      <c r="B325" s="4" t="s">
+      <c r="B325" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C325" s="3">
@@ -8602,7 +8605,7 @@
       <c r="A326" s="1">
         <v>20</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="B326" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C326" s="3">
@@ -8623,7 +8626,7 @@
       <c r="A327" s="1">
         <v>20</v>
       </c>
-      <c r="B327" s="4" t="s">
+      <c r="B327" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C327" s="3">
@@ -8644,7 +8647,7 @@
       <c r="A328" s="1">
         <v>20</v>
       </c>
-      <c r="B328" s="4" t="s">
+      <c r="B328" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C328" s="3">
@@ -8665,7 +8668,7 @@
       <c r="A329" s="1">
         <v>20</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="B329" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C329" s="3">
@@ -8686,7 +8689,7 @@
       <c r="A330" s="1">
         <v>21</v>
       </c>
-      <c r="B330" s="4" t="s">
+      <c r="B330" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C330" s="3">
@@ -8707,7 +8710,7 @@
       <c r="A331" s="1">
         <v>21</v>
       </c>
-      <c r="B331" s="4" t="s">
+      <c r="B331" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C331" s="3">
@@ -8728,7 +8731,7 @@
       <c r="A332" s="1">
         <v>21</v>
       </c>
-      <c r="B332" s="4" t="s">
+      <c r="B332" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C332" s="3">
@@ -8749,7 +8752,7 @@
       <c r="A333" s="1">
         <v>21</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="B333" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C333" s="3">
@@ -8770,7 +8773,7 @@
       <c r="A334" s="1">
         <v>21</v>
       </c>
-      <c r="B334" s="4" t="s">
+      <c r="B334" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C334" s="3">
@@ -8791,7 +8794,7 @@
       <c r="A335" s="1">
         <v>21</v>
       </c>
-      <c r="B335" s="4" t="s">
+      <c r="B335" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C335" s="3">
@@ -8812,7 +8815,7 @@
       <c r="A336" s="1">
         <v>21</v>
       </c>
-      <c r="B336" s="4" t="s">
+      <c r="B336" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C336" s="3">
@@ -8833,7 +8836,7 @@
       <c r="A337" s="1">
         <v>21</v>
       </c>
-      <c r="B337" s="4" t="s">
+      <c r="B337" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C337" s="3">
@@ -8854,7 +8857,7 @@
       <c r="A338" s="1">
         <v>21</v>
       </c>
-      <c r="B338" s="4" t="s">
+      <c r="B338" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C338" s="3">
@@ -8875,7 +8878,7 @@
       <c r="A339" s="1">
         <v>21</v>
       </c>
-      <c r="B339" s="4" t="s">
+      <c r="B339" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C339" s="3">
@@ -8896,7 +8899,7 @@
       <c r="A340" s="1">
         <v>22</v>
       </c>
-      <c r="B340" s="4" t="s">
+      <c r="B340" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C340" s="3">
@@ -8917,7 +8920,7 @@
       <c r="A341" s="1">
         <v>22</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="B341" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C341" s="3">
@@ -8938,7 +8941,7 @@
       <c r="A342" s="1">
         <v>22</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="B342" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C342" s="3">
@@ -8959,7 +8962,7 @@
       <c r="A343" s="1">
         <v>22</v>
       </c>
-      <c r="B343" s="4" t="s">
+      <c r="B343" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C343" s="3">
@@ -8980,7 +8983,7 @@
       <c r="A344" s="1">
         <v>22</v>
       </c>
-      <c r="B344" s="4" t="s">
+      <c r="B344" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C344" s="3">
@@ -9001,7 +9004,7 @@
       <c r="A345" s="1">
         <v>22</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C345" s="3">
@@ -9022,7 +9025,7 @@
       <c r="A346" s="1">
         <v>22</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="B346" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C346" s="3">
@@ -9043,7 +9046,7 @@
       <c r="A347" s="1">
         <v>22</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="B347" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C347" s="3">
@@ -9064,7 +9067,7 @@
       <c r="A348" s="1">
         <v>22</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C348" s="3">
@@ -9085,7 +9088,7 @@
       <c r="A349" s="1">
         <v>22</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="B349" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C349" s="3">
@@ -9106,7 +9109,7 @@
       <c r="A350" s="1">
         <v>23</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C350" s="3">
@@ -9127,7 +9130,7 @@
       <c r="A351" s="1">
         <v>23</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="B351" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C351" s="3">
@@ -9148,7 +9151,7 @@
       <c r="A352" s="1">
         <v>23</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C352" s="3">
@@ -9169,7 +9172,7 @@
       <c r="A353" s="1">
         <v>23</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="B353" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C353" s="3">
@@ -9190,7 +9193,7 @@
       <c r="A354" s="1">
         <v>23</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C354" s="3">
@@ -9211,7 +9214,7 @@
       <c r="A355" s="1">
         <v>23</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="B355" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C355" s="3">
@@ -9232,7 +9235,7 @@
       <c r="A356" s="1">
         <v>23</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C356" s="3">
@@ -9253,7 +9256,7 @@
       <c r="A357" s="1">
         <v>23</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C357" s="3">
@@ -9274,7 +9277,7 @@
       <c r="A358" s="1">
         <v>24</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C358" s="3">
@@ -9295,7 +9298,7 @@
       <c r="A359" s="1">
         <v>24</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C359" s="3">
@@ -9316,7 +9319,7 @@
       <c r="A360" s="1">
         <v>24</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C360" s="3">
@@ -9337,7 +9340,7 @@
       <c r="A361" s="1">
         <v>24</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C361" s="3">
@@ -9358,7 +9361,7 @@
       <c r="A362" s="1">
         <v>24</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C362" s="3">
@@ -9379,7 +9382,7 @@
       <c r="A363" s="1">
         <v>24</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="B363" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C363" s="3">
@@ -9400,7 +9403,7 @@
       <c r="A364" s="1">
         <v>24</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C364" s="3">
@@ -9421,7 +9424,7 @@
       <c r="A365" s="1">
         <v>24</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C365" s="3">
@@ -9442,7 +9445,7 @@
       <c r="A366" s="1">
         <v>24</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C366" s="3">
@@ -9463,7 +9466,7 @@
       <c r="A367" s="1">
         <v>24</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C367" s="3">
@@ -9484,7 +9487,7 @@
       <c r="A368" s="1">
         <v>25</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B368" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C368" s="3">
@@ -9505,7 +9508,7 @@
       <c r="A369" s="1">
         <v>25</v>
       </c>
-      <c r="B369" s="4" t="s">
+      <c r="B369" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C369" s="3">
@@ -9526,7 +9529,7 @@
       <c r="A370" s="1">
         <v>25</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B370" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C370" s="3">
@@ -9547,7 +9550,7 @@
       <c r="A371" s="1">
         <v>25</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B371" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C371" s="3">
@@ -9568,7 +9571,7 @@
       <c r="A372" s="1">
         <v>25</v>
       </c>
-      <c r="B372" s="4" t="s">
+      <c r="B372" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C372" s="3">
@@ -9589,7 +9592,7 @@
       <c r="A373" s="1">
         <v>25</v>
       </c>
-      <c r="B373" s="4" t="s">
+      <c r="B373" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C373" s="3">
@@ -9610,7 +9613,7 @@
       <c r="A374" s="1">
         <v>25</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="B374" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C374" s="3">
@@ -9631,7 +9634,7 @@
       <c r="A375" s="1">
         <v>25</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="B375" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C375" s="3">
@@ -9652,7 +9655,7 @@
       <c r="A376" s="1">
         <v>26</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B376" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C376" s="3">
@@ -9673,7 +9676,7 @@
       <c r="A377" s="1">
         <v>26</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C377" s="3">
@@ -9694,7 +9697,7 @@
       <c r="A378" s="1">
         <v>26</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B378" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C378" s="3">
@@ -9715,7 +9718,7 @@
       <c r="A379" s="1">
         <v>26</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C379" s="3">
@@ -9736,7 +9739,7 @@
       <c r="A380" s="1">
         <v>26</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B380" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C380" s="3">
@@ -9757,7 +9760,7 @@
       <c r="A381" s="1">
         <v>26</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B381" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C381" s="3">
@@ -9778,7 +9781,7 @@
       <c r="A382" s="1">
         <v>26</v>
       </c>
-      <c r="B382" s="4" t="s">
+      <c r="B382" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C382" s="3">
@@ -9799,7 +9802,7 @@
       <c r="A383" s="1">
         <v>26</v>
       </c>
-      <c r="B383" s="4" t="s">
+      <c r="B383" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C383" s="3">
@@ -9820,7 +9823,7 @@
       <c r="A384" s="1">
         <v>26</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="B384" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C384" s="3">
@@ -9841,7 +9844,7 @@
       <c r="A385" s="1">
         <v>26</v>
       </c>
-      <c r="B385" s="4" t="s">
+      <c r="B385" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C385" s="3">
@@ -9862,7 +9865,7 @@
       <c r="A386" s="1">
         <v>27</v>
       </c>
-      <c r="B386" s="4" t="s">
+      <c r="B386" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C386" s="3">
@@ -9883,7 +9886,7 @@
       <c r="A387" s="1">
         <v>27</v>
       </c>
-      <c r="B387" s="4" t="s">
+      <c r="B387" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C387" s="3">
@@ -9904,7 +9907,7 @@
       <c r="A388" s="1">
         <v>27</v>
       </c>
-      <c r="B388" s="4" t="s">
+      <c r="B388" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C388" s="3">
@@ -9925,7 +9928,7 @@
       <c r="A389" s="1">
         <v>27</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="B389" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C389" s="3">
@@ -9946,7 +9949,7 @@
       <c r="A390" s="1">
         <v>27</v>
       </c>
-      <c r="B390" s="4" t="s">
+      <c r="B390" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C390" s="3">
@@ -9967,7 +9970,7 @@
       <c r="A391" s="1">
         <v>27</v>
       </c>
-      <c r="B391" s="4" t="s">
+      <c r="B391" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C391" s="3">
@@ -9988,7 +9991,7 @@
       <c r="A392" s="1">
         <v>27</v>
       </c>
-      <c r="B392" s="4" t="s">
+      <c r="B392" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C392" s="3">
@@ -10009,7 +10012,7 @@
       <c r="A393" s="1">
         <v>27</v>
       </c>
-      <c r="B393" s="4" t="s">
+      <c r="B393" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C393" s="3">
@@ -10030,7 +10033,7 @@
       <c r="A394" s="1">
         <v>27</v>
       </c>
-      <c r="B394" s="4" t="s">
+      <c r="B394" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C394" s="3">
@@ -10051,7 +10054,7 @@
       <c r="A395" s="1">
         <v>28</v>
       </c>
-      <c r="B395" s="4" t="s">
+      <c r="B395" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C395" s="3">
@@ -10072,7 +10075,7 @@
       <c r="A396" s="1">
         <v>28</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B396" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C396" s="3">
@@ -10093,7 +10096,7 @@
       <c r="A397" s="1">
         <v>28</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B397" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C397" s="3">
@@ -10114,7 +10117,7 @@
       <c r="A398" s="1">
         <v>28</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="B398" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C398" s="3">
@@ -10135,7 +10138,7 @@
       <c r="A399" s="1">
         <v>28</v>
       </c>
-      <c r="B399" s="4" t="s">
+      <c r="B399" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C399" s="3">
@@ -10156,7 +10159,7 @@
       <c r="A400" s="1">
         <v>28</v>
       </c>
-      <c r="B400" s="4" t="s">
+      <c r="B400" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C400" s="3">
@@ -10177,7 +10180,7 @@
       <c r="A401" s="1">
         <v>28</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C401" s="3">
@@ -10198,7 +10201,7 @@
       <c r="A402" s="1">
         <v>28</v>
       </c>
-      <c r="B402" s="4" t="s">
+      <c r="B402" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C402" s="3">
@@ -10219,7 +10222,7 @@
       <c r="A403" s="1">
         <v>28</v>
       </c>
-      <c r="B403" s="4" t="s">
+      <c r="B403" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C403" s="3">
@@ -10240,7 +10243,7 @@
       <c r="A404" s="1">
         <v>28</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B404" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C404" s="3">
@@ -10261,7 +10264,7 @@
       <c r="A405" s="1">
         <v>28</v>
       </c>
-      <c r="B405" s="4" t="s">
+      <c r="B405" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C405" s="3">
@@ -10282,7 +10285,7 @@
       <c r="A406" s="1">
         <v>28</v>
       </c>
-      <c r="B406" s="4" t="s">
+      <c r="B406" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C406" s="3">
@@ -10303,7 +10306,7 @@
       <c r="A407" s="1">
         <v>29</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B407" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C407" s="3">
@@ -10324,7 +10327,7 @@
       <c r="A408" s="1">
         <v>29</v>
       </c>
-      <c r="B408" s="4" t="s">
+      <c r="B408" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C408" s="3">
@@ -10345,7 +10348,7 @@
       <c r="A409" s="1">
         <v>29</v>
       </c>
-      <c r="B409" s="4" t="s">
+      <c r="B409" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C409" s="3">
@@ -10366,7 +10369,7 @@
       <c r="A410" s="1">
         <v>29</v>
       </c>
-      <c r="B410" s="4" t="s">
+      <c r="B410" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C410" s="3">
@@ -10387,7 +10390,7 @@
       <c r="A411" s="1">
         <v>29</v>
       </c>
-      <c r="B411" s="4" t="s">
+      <c r="B411" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C411" s="3">
@@ -10408,7 +10411,7 @@
       <c r="A412" s="1">
         <v>29</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B412" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C412" s="3">
@@ -10429,7 +10432,7 @@
       <c r="A413" s="1">
         <v>29</v>
       </c>
-      <c r="B413" s="4" t="s">
+      <c r="B413" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C413" s="3">
@@ -10450,7 +10453,7 @@
       <c r="A414" s="1">
         <v>29</v>
       </c>
-      <c r="B414" s="4" t="s">
+      <c r="B414" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C414" s="3">
@@ -10471,7 +10474,7 @@
       <c r="A415" s="1">
         <v>29</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B415" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C415" s="3">
@@ -10492,7 +10495,7 @@
       <c r="A416" s="1">
         <v>30</v>
       </c>
-      <c r="B416" s="4" t="s">
+      <c r="B416" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C416" s="3">
@@ -10513,7 +10516,7 @@
       <c r="A417" s="1">
         <v>30</v>
       </c>
-      <c r="B417" s="4" t="s">
+      <c r="B417" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C417" s="3">
@@ -10534,7 +10537,7 @@
       <c r="A418" s="1">
         <v>30</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="B418" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C418" s="3">
@@ -10555,7 +10558,7 @@
       <c r="A419" s="1">
         <v>30</v>
       </c>
-      <c r="B419" s="4" t="s">
+      <c r="B419" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C419" s="3">
@@ -10576,7 +10579,7 @@
       <c r="A420" s="1">
         <v>30</v>
       </c>
-      <c r="B420" s="4" t="s">
+      <c r="B420" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C420" s="3">
@@ -10597,7 +10600,7 @@
       <c r="A421" s="1">
         <v>30</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C421" s="3">
@@ -10618,7 +10621,7 @@
       <c r="A422" s="1">
         <v>30</v>
       </c>
-      <c r="B422" s="4" t="s">
+      <c r="B422" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C422" s="3">
@@ -10639,7 +10642,7 @@
       <c r="A423" s="1">
         <v>31</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B423" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C423" s="3">
@@ -10660,7 +10663,7 @@
       <c r="A424" s="1">
         <v>31</v>
       </c>
-      <c r="B424" s="4" t="s">
+      <c r="B424" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C424" s="3">
@@ -10681,7 +10684,7 @@
       <c r="A425" s="1">
         <v>31</v>
       </c>
-      <c r="B425" s="4" t="s">
+      <c r="B425" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C425" s="3">
@@ -10702,7 +10705,7 @@
       <c r="A426" s="1">
         <v>31</v>
       </c>
-      <c r="B426" s="4" t="s">
+      <c r="B426" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C426" s="3">
@@ -10723,7 +10726,7 @@
       <c r="A427" s="1">
         <v>32</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B427" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C427" s="3">
@@ -10744,7 +10747,7 @@
       <c r="A428" s="1">
         <v>32</v>
       </c>
-      <c r="B428" s="4" t="s">
+      <c r="B428" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C428" s="3">
@@ -10765,7 +10768,7 @@
       <c r="A429" s="1">
         <v>32</v>
       </c>
-      <c r="B429" s="4" t="s">
+      <c r="B429" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C429" s="3">
@@ -10786,7 +10789,7 @@
       <c r="A430" s="1">
         <v>33</v>
       </c>
-      <c r="B430" s="4" t="s">
+      <c r="B430" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C430" s="3">
@@ -10807,7 +10810,7 @@
       <c r="A431" s="1">
         <v>33</v>
       </c>
-      <c r="B431" s="4" t="s">
+      <c r="B431" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C431" s="3">
@@ -10828,7 +10831,7 @@
       <c r="A432" s="1">
         <v>33</v>
       </c>
-      <c r="B432" s="4" t="s">
+      <c r="B432" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C432" s="3">
@@ -10849,7 +10852,7 @@
       <c r="A433" s="1">
         <v>33</v>
       </c>
-      <c r="B433" s="4" t="s">
+      <c r="B433" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C433" s="3">
@@ -10870,7 +10873,7 @@
       <c r="A434" s="1">
         <v>33</v>
       </c>
-      <c r="B434" s="4" t="s">
+      <c r="B434" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C434" s="3">
@@ -10891,7 +10894,7 @@
       <c r="A435" s="1">
         <v>33</v>
       </c>
-      <c r="B435" s="4" t="s">
+      <c r="B435" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C435" s="3">
@@ -10912,7 +10915,7 @@
       <c r="A436" s="1">
         <v>33</v>
       </c>
-      <c r="B436" s="4" t="s">
+      <c r="B436" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C436" s="3">
@@ -10933,7 +10936,7 @@
       <c r="A437" s="1">
         <v>33</v>
       </c>
-      <c r="B437" s="4" t="s">
+      <c r="B437" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C437" s="3">
@@ -10954,7 +10957,7 @@
       <c r="A438" s="1">
         <v>33</v>
       </c>
-      <c r="B438" s="4" t="s">
+      <c r="B438" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C438" s="3">
@@ -10975,7 +10978,7 @@
       <c r="A439" s="1">
         <v>33</v>
       </c>
-      <c r="B439" s="4" t="s">
+      <c r="B439" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C439" s="3">
@@ -10996,7 +10999,7 @@
       <c r="A440" s="1">
         <v>34</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C440" s="3">
@@ -11017,7 +11020,7 @@
       <c r="A441" s="1">
         <v>34</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C441" s="3">
@@ -11038,7 +11041,7 @@
       <c r="A442" s="1">
         <v>34</v>
       </c>
-      <c r="B442" s="4" t="s">
+      <c r="B442" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C442" s="3">
@@ -11059,7 +11062,7 @@
       <c r="A443" s="1">
         <v>34</v>
       </c>
-      <c r="B443" s="4" t="s">
+      <c r="B443" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C443" s="3">
@@ -11080,7 +11083,7 @@
       <c r="A444" s="1">
         <v>34</v>
       </c>
-      <c r="B444" s="4" t="s">
+      <c r="B444" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C444" s="3">
@@ -11101,7 +11104,7 @@
       <c r="A445" s="1">
         <v>34</v>
       </c>
-      <c r="B445" s="4" t="s">
+      <c r="B445" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C445" s="3">
@@ -11122,7 +11125,7 @@
       <c r="A446" s="1">
         <v>34</v>
       </c>
-      <c r="B446" s="4" t="s">
+      <c r="B446" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C446" s="3">
@@ -11143,7 +11146,7 @@
       <c r="A447" s="1">
         <v>35</v>
       </c>
-      <c r="B447" s="4" t="s">
+      <c r="B447" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C447" s="3">
@@ -11164,7 +11167,7 @@
       <c r="A448" s="1">
         <v>35</v>
       </c>
-      <c r="B448" s="4" t="s">
+      <c r="B448" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C448" s="3">
@@ -11185,7 +11188,7 @@
       <c r="A449" s="1">
         <v>35</v>
       </c>
-      <c r="B449" s="4" t="s">
+      <c r="B449" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C449" s="3">
@@ -11206,7 +11209,7 @@
       <c r="A450" s="1">
         <v>35</v>
       </c>
-      <c r="B450" s="4" t="s">
+      <c r="B450" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C450" s="3">
@@ -11227,7 +11230,7 @@
       <c r="A451" s="1">
         <v>35</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C451" s="3">
@@ -11248,7 +11251,7 @@
       <c r="A452" s="1">
         <v>35</v>
       </c>
-      <c r="B452" s="4" t="s">
+      <c r="B452" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C452" s="3">
@@ -11269,7 +11272,7 @@
       <c r="A453" s="1">
         <v>35</v>
       </c>
-      <c r="B453" s="4" t="s">
+      <c r="B453" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C453" s="3">
@@ -11290,7 +11293,7 @@
       <c r="A454" s="1">
         <v>36</v>
       </c>
-      <c r="B454" s="4" t="s">
+      <c r="B454" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C454" s="3">
@@ -11311,7 +11314,7 @@
       <c r="A455" s="1">
         <v>36</v>
       </c>
-      <c r="B455" s="4" t="s">
+      <c r="B455" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C455" s="3">
@@ -11332,7 +11335,7 @@
       <c r="A456" s="1">
         <v>36</v>
       </c>
-      <c r="B456" s="4" t="s">
+      <c r="B456" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C456" s="3">
@@ -11353,7 +11356,7 @@
       <c r="A457" s="1">
         <v>36</v>
       </c>
-      <c r="B457" s="4" t="s">
+      <c r="B457" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C457" s="3">
@@ -11374,7 +11377,7 @@
       <c r="A458" s="1">
         <v>36</v>
       </c>
-      <c r="B458" s="4" t="s">
+      <c r="B458" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C458" s="3">
@@ -11395,7 +11398,7 @@
       <c r="A459" s="1">
         <v>36</v>
       </c>
-      <c r="B459" s="4" t="s">
+      <c r="B459" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C459" s="3">
@@ -11416,7 +11419,7 @@
       <c r="A460" s="1">
         <v>37</v>
       </c>
-      <c r="B460" s="4" t="s">
+      <c r="B460" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C460" s="3">
@@ -11437,7 +11440,7 @@
       <c r="A461" s="1">
         <v>37</v>
       </c>
-      <c r="B461" s="4" t="s">
+      <c r="B461" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C461" s="3">
@@ -11458,7 +11461,7 @@
       <c r="A462" s="1">
         <v>37</v>
       </c>
-      <c r="B462" s="4" t="s">
+      <c r="B462" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C462" s="3">
@@ -11479,7 +11482,7 @@
       <c r="A463" s="1">
         <v>37</v>
       </c>
-      <c r="B463" s="4" t="s">
+      <c r="B463" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C463" s="3">
@@ -11500,7 +11503,7 @@
       <c r="A464" s="1">
         <v>37</v>
       </c>
-      <c r="B464" s="4" t="s">
+      <c r="B464" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C464" s="3">
@@ -11521,7 +11524,7 @@
       <c r="A465" s="1">
         <v>37</v>
       </c>
-      <c r="B465" s="4" t="s">
+      <c r="B465" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C465" s="3">
@@ -11542,7 +11545,7 @@
       <c r="A466" s="1">
         <v>37</v>
       </c>
-      <c r="B466" s="4" t="s">
+      <c r="B466" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C466" s="3">
@@ -11563,7 +11566,7 @@
       <c r="A467" s="1">
         <v>38</v>
       </c>
-      <c r="B467" s="4" t="s">
+      <c r="B467" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C467" s="3">
@@ -11584,7 +11587,7 @@
       <c r="A468" s="1">
         <v>38</v>
       </c>
-      <c r="B468" s="4" t="s">
+      <c r="B468" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C468" s="3">
@@ -11605,7 +11608,7 @@
       <c r="A469" s="1">
         <v>38</v>
       </c>
-      <c r="B469" s="4" t="s">
+      <c r="B469" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C469" s="3">
@@ -11626,7 +11629,7 @@
       <c r="A470" s="1">
         <v>38</v>
       </c>
-      <c r="B470" s="4" t="s">
+      <c r="B470" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C470" s="3">
@@ -11647,7 +11650,7 @@
       <c r="A471" s="1">
         <v>38</v>
       </c>
-      <c r="B471" s="4" t="s">
+      <c r="B471" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C471" s="3">
@@ -11668,7 +11671,7 @@
       <c r="A472" s="1">
         <v>38</v>
       </c>
-      <c r="B472" s="4" t="s">
+      <c r="B472" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C472" s="3">
@@ -11689,7 +11692,7 @@
       <c r="A473" s="1">
         <v>39</v>
       </c>
-      <c r="B473" s="4" t="s">
+      <c r="B473" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C473" s="3">
@@ -11710,7 +11713,7 @@
       <c r="A474" s="1">
         <v>39</v>
       </c>
-      <c r="B474" s="4" t="s">
+      <c r="B474" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C474" s="3">
@@ -11731,7 +11734,7 @@
       <c r="A475" s="1">
         <v>39</v>
       </c>
-      <c r="B475" s="4" t="s">
+      <c r="B475" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C475" s="3">
@@ -11752,7 +11755,7 @@
       <c r="A476" s="1">
         <v>39</v>
       </c>
-      <c r="B476" s="4" t="s">
+      <c r="B476" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C476" s="3">
@@ -11773,7 +11776,7 @@
       <c r="A477" s="1">
         <v>39</v>
       </c>
-      <c r="B477" s="4" t="s">
+      <c r="B477" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C477" s="3">
@@ -11794,7 +11797,7 @@
       <c r="A478" s="1">
         <v>39</v>
       </c>
-      <c r="B478" s="4" t="s">
+      <c r="B478" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C478" s="3">
@@ -11815,7 +11818,7 @@
       <c r="A479" s="1">
         <v>39</v>
       </c>
-      <c r="B479" s="4" t="s">
+      <c r="B479" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C479" s="3">
@@ -11836,7 +11839,7 @@
       <c r="A480" s="1">
         <v>39</v>
       </c>
-      <c r="B480" s="4" t="s">
+      <c r="B480" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C480" s="3">
@@ -11857,7 +11860,7 @@
       <c r="A481" s="1">
         <v>39</v>
       </c>
-      <c r="B481" s="4" t="s">
+      <c r="B481" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C481" s="3">
@@ -11878,7 +11881,7 @@
       <c r="A482" s="1">
         <v>39</v>
       </c>
-      <c r="B482" s="4" t="s">
+      <c r="B482" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C482" s="3">
@@ -11899,7 +11902,7 @@
       <c r="A483" s="1">
         <v>40</v>
       </c>
-      <c r="B483" s="4" t="s">
+      <c r="B483" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C483" s="3">
@@ -11920,7 +11923,7 @@
       <c r="A484" s="1">
         <v>40</v>
       </c>
-      <c r="B484" s="4" t="s">
+      <c r="B484" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C484" s="3">
@@ -11941,7 +11944,7 @@
       <c r="A485" s="1">
         <v>40</v>
       </c>
-      <c r="B485" s="4" t="s">
+      <c r="B485" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C485" s="3">
@@ -11962,7 +11965,7 @@
       <c r="A486" s="1">
         <v>40</v>
       </c>
-      <c r="B486" s="4" t="s">
+      <c r="B486" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C486" s="3">
@@ -11983,7 +11986,7 @@
       <c r="A487" s="1">
         <v>40</v>
       </c>
-      <c r="B487" s="4" t="s">
+      <c r="B487" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C487" s="3">
@@ -12004,7 +12007,7 @@
       <c r="A488" s="1">
         <v>40</v>
       </c>
-      <c r="B488" s="4" t="s">
+      <c r="B488" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C488" s="3">
@@ -12025,7 +12028,7 @@
       <c r="A489" s="1">
         <v>40</v>
       </c>
-      <c r="B489" s="4" t="s">
+      <c r="B489" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C489" s="3">
@@ -12046,7 +12049,7 @@
       <c r="A490" s="1">
         <v>40</v>
       </c>
-      <c r="B490" s="4" t="s">
+      <c r="B490" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C490" s="3">
@@ -12067,7 +12070,7 @@
       <c r="A491" s="1">
         <v>40</v>
       </c>
-      <c r="B491" s="4" t="s">
+      <c r="B491" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C491" s="3">
@@ -12088,7 +12091,7 @@
       <c r="A492" s="1">
         <v>40</v>
       </c>
-      <c r="B492" s="4" t="s">
+      <c r="B492" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C492" s="3">
@@ -12109,7 +12112,7 @@
       <c r="A493" s="1">
         <v>41</v>
       </c>
-      <c r="B493" s="4" t="s">
+      <c r="B493" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C493" s="3">
@@ -12130,7 +12133,7 @@
       <c r="A494" s="1">
         <v>41</v>
       </c>
-      <c r="B494" s="4" t="s">
+      <c r="B494" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C494" s="3">
@@ -12151,7 +12154,7 @@
       <c r="A495" s="1">
         <v>41</v>
       </c>
-      <c r="B495" s="4" t="s">
+      <c r="B495" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C495" s="3">
@@ -12172,7 +12175,7 @@
       <c r="A496" s="1">
         <v>41</v>
       </c>
-      <c r="B496" s="4" t="s">
+      <c r="B496" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C496" s="3">
@@ -12193,7 +12196,7 @@
       <c r="A497" s="1">
         <v>41</v>
       </c>
-      <c r="B497" s="4" t="s">
+      <c r="B497" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C497" s="3">
@@ -12214,7 +12217,7 @@
       <c r="A498" s="1">
         <v>41</v>
       </c>
-      <c r="B498" s="4" t="s">
+      <c r="B498" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C498" s="3">
@@ -12235,7 +12238,7 @@
       <c r="A499" s="1">
         <v>42</v>
       </c>
-      <c r="B499" s="4" t="s">
+      <c r="B499" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C499" s="3">
@@ -12256,7 +12259,7 @@
       <c r="A500" s="1">
         <v>42</v>
       </c>
-      <c r="B500" s="4" t="s">
+      <c r="B500" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C500" s="3">
@@ -12277,7 +12280,7 @@
       <c r="A501" s="1">
         <v>42</v>
       </c>
-      <c r="B501" s="4" t="s">
+      <c r="B501" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C501" s="3">
@@ -12298,7 +12301,7 @@
       <c r="A502" s="1">
         <v>42</v>
       </c>
-      <c r="B502" s="4" t="s">
+      <c r="B502" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C502" s="3">
@@ -12319,7 +12322,7 @@
       <c r="A503" s="1">
         <v>42</v>
       </c>
-      <c r="B503" s="4" t="s">
+      <c r="B503" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C503" s="3">
@@ -12340,7 +12343,7 @@
       <c r="A504" s="1">
         <v>42</v>
       </c>
-      <c r="B504" s="4" t="s">
+      <c r="B504" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C504" s="3">
@@ -12361,7 +12364,7 @@
       <c r="A505" s="1">
         <v>42</v>
       </c>
-      <c r="B505" s="4" t="s">
+      <c r="B505" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C505" s="3">
@@ -12382,7 +12385,7 @@
       <c r="A506" s="1">
         <v>43</v>
       </c>
-      <c r="B506" s="4" t="s">
+      <c r="B506" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C506" s="3">
@@ -12403,7 +12406,7 @@
       <c r="A507" s="1">
         <v>43</v>
       </c>
-      <c r="B507" s="4" t="s">
+      <c r="B507" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C507" s="3">
@@ -12424,7 +12427,7 @@
       <c r="A508" s="1">
         <v>43</v>
       </c>
-      <c r="B508" s="4" t="s">
+      <c r="B508" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C508" s="3">
@@ -12445,7 +12448,7 @@
       <c r="A509" s="1">
         <v>43</v>
       </c>
-      <c r="B509" s="4" t="s">
+      <c r="B509" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C509" s="3">
@@ -12466,7 +12469,7 @@
       <c r="A510" s="1">
         <v>43</v>
       </c>
-      <c r="B510" s="4" t="s">
+      <c r="B510" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C510" s="3">
@@ -12487,7 +12490,7 @@
       <c r="A511" s="1">
         <v>43</v>
       </c>
-      <c r="B511" s="4" t="s">
+      <c r="B511" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C511" s="3">
@@ -12508,7 +12511,7 @@
       <c r="A512" s="1">
         <v>43</v>
       </c>
-      <c r="B512" s="4" t="s">
+      <c r="B512" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C512" s="3">
@@ -12529,7 +12532,7 @@
       <c r="A513" s="1">
         <v>44</v>
       </c>
-      <c r="B513" s="4" t="s">
+      <c r="B513" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C513" s="3">
@@ -12550,7 +12553,7 @@
       <c r="A514" s="1">
         <v>44</v>
       </c>
-      <c r="B514" s="4" t="s">
+      <c r="B514" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C514" s="3">
@@ -12571,7 +12574,7 @@
       <c r="A515" s="1">
         <v>44</v>
       </c>
-      <c r="B515" s="4" t="s">
+      <c r="B515" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C515" s="3">
@@ -12592,7 +12595,7 @@
       <c r="A516" s="1">
         <v>45</v>
       </c>
-      <c r="B516" s="4" t="s">
+      <c r="B516" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C516" s="3">
@@ -12613,7 +12616,7 @@
       <c r="A517" s="1">
         <v>45</v>
       </c>
-      <c r="B517" s="4" t="s">
+      <c r="B517" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C517" s="3">
@@ -12634,7 +12637,7 @@
       <c r="A518" s="1">
         <v>45</v>
       </c>
-      <c r="B518" s="4" t="s">
+      <c r="B518" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C518" s="3">
@@ -12655,7 +12658,7 @@
       <c r="A519" s="1">
         <v>45</v>
       </c>
-      <c r="B519" s="4" t="s">
+      <c r="B519" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C519" s="3">
@@ -12676,7 +12679,7 @@
       <c r="A520" s="1">
         <v>46</v>
       </c>
-      <c r="B520" s="4" t="s">
+      <c r="B520" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C520" s="3">
@@ -12697,7 +12700,7 @@
       <c r="A521" s="1">
         <v>46</v>
       </c>
-      <c r="B521" s="4" t="s">
+      <c r="B521" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C521" s="3">
@@ -12718,7 +12721,7 @@
       <c r="A522" s="1">
         <v>46</v>
       </c>
-      <c r="B522" s="4" t="s">
+      <c r="B522" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C522" s="3">
@@ -12739,7 +12742,7 @@
       <c r="A523" s="1">
         <v>46</v>
       </c>
-      <c r="B523" s="4" t="s">
+      <c r="B523" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C523" s="3">
@@ -12760,7 +12763,7 @@
       <c r="A524" s="1">
         <v>46</v>
       </c>
-      <c r="B524" s="4" t="s">
+      <c r="B524" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C524" s="3">
@@ -12781,7 +12784,7 @@
       <c r="A525" s="1">
         <v>47</v>
       </c>
-      <c r="B525" s="4" t="s">
+      <c r="B525" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C525" s="3">
@@ -12802,7 +12805,7 @@
       <c r="A526" s="1">
         <v>47</v>
       </c>
-      <c r="B526" s="4" t="s">
+      <c r="B526" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C526" s="3">
@@ -12823,7 +12826,7 @@
       <c r="A527" s="1">
         <v>47</v>
       </c>
-      <c r="B527" s="4" t="s">
+      <c r="B527" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C527" s="3">
@@ -12844,7 +12847,7 @@
       <c r="A528" s="1">
         <v>47</v>
       </c>
-      <c r="B528" s="4" t="s">
+      <c r="B528" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C528" s="3">
@@ -12865,7 +12868,7 @@
       <c r="A529" s="1">
         <v>48</v>
       </c>
-      <c r="B529" s="4" t="s">
+      <c r="B529" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C529" s="3">
@@ -12886,7 +12889,7 @@
       <c r="A530" s="1">
         <v>48</v>
       </c>
-      <c r="B530" s="4" t="s">
+      <c r="B530" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C530" s="3">
@@ -12907,7 +12910,7 @@
       <c r="A531" s="1">
         <v>48</v>
       </c>
-      <c r="B531" s="4" t="s">
+      <c r="B531" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C531" s="3">
@@ -12928,7 +12931,7 @@
       <c r="A532" s="1">
         <v>48</v>
       </c>
-      <c r="B532" s="4" t="s">
+      <c r="B532" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C532" s="3">
@@ -12949,7 +12952,7 @@
       <c r="A533" s="1">
         <v>48</v>
       </c>
-      <c r="B533" s="4" t="s">
+      <c r="B533" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C533" s="3">
@@ -12970,7 +12973,7 @@
       <c r="A534" s="1">
         <v>49</v>
       </c>
-      <c r="B534" s="4" t="s">
+      <c r="B534" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C534" s="3">
@@ -12991,7 +12994,7 @@
       <c r="A535" s="1">
         <v>49</v>
       </c>
-      <c r="B535" s="4" t="s">
+      <c r="B535" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C535" s="3">
@@ -13012,7 +13015,7 @@
       <c r="A536" s="1">
         <v>49</v>
       </c>
-      <c r="B536" s="4" t="s">
+      <c r="B536" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C536" s="3">
@@ -13033,7 +13036,7 @@
       <c r="A537" s="1">
         <v>50</v>
       </c>
-      <c r="B537" s="4" t="s">
+      <c r="B537" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C537" s="3">
@@ -13054,7 +13057,7 @@
       <c r="A538" s="1">
         <v>50</v>
       </c>
-      <c r="B538" s="4" t="s">
+      <c r="B538" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C538" s="3">
@@ -13075,7 +13078,7 @@
       <c r="A539" s="1">
         <v>50</v>
       </c>
-      <c r="B539" s="4" t="s">
+      <c r="B539" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C539" s="3">
@@ -13096,7 +13099,7 @@
       <c r="A540" s="1">
         <v>51</v>
       </c>
-      <c r="B540" s="4" t="s">
+      <c r="B540" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C540" s="3">
@@ -13117,7 +13120,7 @@
       <c r="A541" s="1">
         <v>51</v>
       </c>
-      <c r="B541" s="4" t="s">
+      <c r="B541" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C541" s="3">
@@ -13138,7 +13141,7 @@
       <c r="A542" s="1">
         <v>51</v>
       </c>
-      <c r="B542" s="4" t="s">
+      <c r="B542" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C542" s="3">
@@ -13159,7 +13162,7 @@
       <c r="A543" s="1">
         <v>51</v>
       </c>
-      <c r="B543" s="4" t="s">
+      <c r="B543" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C543" s="3">
@@ -13180,7 +13183,7 @@
       <c r="A544" s="1">
         <v>52</v>
       </c>
-      <c r="B544" s="4" t="s">
+      <c r="B544" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C544" s="3">
@@ -13201,7 +13204,7 @@
       <c r="A545" s="1">
         <v>52</v>
       </c>
-      <c r="B545" s="4" t="s">
+      <c r="B545" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C545" s="3">
@@ -13222,7 +13225,7 @@
       <c r="A546" s="1">
         <v>52</v>
       </c>
-      <c r="B546" s="4" t="s">
+      <c r="B546" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C546" s="3">
@@ -13243,7 +13246,7 @@
       <c r="A547" s="1">
         <v>53</v>
       </c>
-      <c r="B547" s="4" t="s">
+      <c r="B547" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C547" s="3">
@@ -13264,7 +13267,7 @@
       <c r="A548" s="1">
         <v>53</v>
       </c>
-      <c r="B548" s="4" t="s">
+      <c r="B548" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C548" s="3">
@@ -13285,7 +13288,7 @@
       <c r="A549" s="1">
         <v>53</v>
       </c>
-      <c r="B549" s="4" t="s">
+      <c r="B549" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C549" s="3">
@@ -13306,7 +13309,7 @@
       <c r="A550" s="1">
         <v>54</v>
       </c>
-      <c r="B550" s="4" t="s">
+      <c r="B550" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C550" s="3">
@@ -13327,7 +13330,7 @@
       <c r="A551" s="1">
         <v>54</v>
       </c>
-      <c r="B551" s="4" t="s">
+      <c r="B551" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C551" s="3">
@@ -13348,7 +13351,7 @@
       <c r="A552" s="1">
         <v>54</v>
       </c>
-      <c r="B552" s="4" t="s">
+      <c r="B552" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C552" s="3">
@@ -13369,7 +13372,7 @@
       <c r="A553" s="1">
         <v>54</v>
       </c>
-      <c r="B553" s="4" t="s">
+      <c r="B553" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C553" s="3">
@@ -13390,7 +13393,7 @@
       <c r="A554" s="1">
         <v>55</v>
       </c>
-      <c r="B554" s="4" t="s">
+      <c r="B554" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C554" s="3">
@@ -13411,7 +13414,7 @@
       <c r="A555" s="1">
         <v>55</v>
       </c>
-      <c r="B555" s="4" t="s">
+      <c r="B555" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C555" s="3">
@@ -13432,7 +13435,7 @@
       <c r="A556" s="1">
         <v>55</v>
       </c>
-      <c r="B556" s="4" t="s">
+      <c r="B556" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C556" s="3">
@@ -13453,7 +13456,7 @@
       <c r="A557" s="1">
         <v>55</v>
       </c>
-      <c r="B557" s="4" t="s">
+      <c r="B557" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C557" s="3">
@@ -13474,7 +13477,7 @@
       <c r="A558" s="1">
         <v>56</v>
       </c>
-      <c r="B558" s="4" t="s">
+      <c r="B558" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C558" s="3">
@@ -13495,7 +13498,7 @@
       <c r="A559" s="1">
         <v>56</v>
       </c>
-      <c r="B559" s="4" t="s">
+      <c r="B559" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C559" s="3">
@@ -13516,7 +13519,7 @@
       <c r="A560" s="1">
         <v>56</v>
       </c>
-      <c r="B560" s="4" t="s">
+      <c r="B560" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C560" s="3">
@@ -13537,7 +13540,7 @@
       <c r="A561" s="1">
         <v>56</v>
       </c>
-      <c r="B561" s="4" t="s">
+      <c r="B561" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C561" s="3">
@@ -13558,7 +13561,7 @@
       <c r="A562" s="1">
         <v>57</v>
       </c>
-      <c r="B562" s="4" t="s">
+      <c r="B562" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C562" s="3">
@@ -13579,7 +13582,7 @@
       <c r="A563" s="1">
         <v>57</v>
       </c>
-      <c r="B563" s="4" t="s">
+      <c r="B563" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C563" s="3">
@@ -13600,7 +13603,7 @@
       <c r="A564" s="1">
         <v>57</v>
       </c>
-      <c r="B564" s="4" t="s">
+      <c r="B564" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C564" s="3">
@@ -13621,7 +13624,7 @@
       <c r="A565" s="1">
         <v>57</v>
       </c>
-      <c r="B565" s="4" t="s">
+      <c r="B565" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C565" s="3">
@@ -13642,7 +13645,7 @@
       <c r="A566" s="1">
         <v>57</v>
       </c>
-      <c r="B566" s="4" t="s">
+      <c r="B566" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C566" s="3">
@@ -13663,7 +13666,7 @@
       <c r="A567" s="1">
         <v>58</v>
       </c>
-      <c r="B567" s="4" t="s">
+      <c r="B567" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C567" s="3">
@@ -13684,7 +13687,7 @@
       <c r="A568" s="1">
         <v>58</v>
       </c>
-      <c r="B568" s="4" t="s">
+      <c r="B568" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C568" s="3">
@@ -13705,7 +13708,7 @@
       <c r="A569" s="1">
         <v>58</v>
       </c>
-      <c r="B569" s="4" t="s">
+      <c r="B569" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C569" s="3">
@@ -13726,7 +13729,7 @@
       <c r="A570" s="1">
         <v>58</v>
       </c>
-      <c r="B570" s="4" t="s">
+      <c r="B570" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C570" s="3">
@@ -13747,7 +13750,7 @@
       <c r="A571" s="1">
         <v>59</v>
       </c>
-      <c r="B571" s="4" t="s">
+      <c r="B571" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C571" s="3">
@@ -13768,7 +13771,7 @@
       <c r="A572" s="1">
         <v>59</v>
       </c>
-      <c r="B572" s="4" t="s">
+      <c r="B572" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C572" s="3">
@@ -13789,7 +13792,7 @@
       <c r="A573" s="1">
         <v>59</v>
       </c>
-      <c r="B573" s="4" t="s">
+      <c r="B573" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C573" s="3">
@@ -13810,7 +13813,7 @@
       <c r="A574" s="1">
         <v>59</v>
       </c>
-      <c r="B574" s="4" t="s">
+      <c r="B574" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C574" s="3">
@@ -13831,7 +13834,7 @@
       <c r="A575" s="1">
         <v>60</v>
       </c>
-      <c r="B575" s="4" t="s">
+      <c r="B575" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C575" s="3">
@@ -13852,7 +13855,7 @@
       <c r="A576" s="1">
         <v>60</v>
       </c>
-      <c r="B576" s="4" t="s">
+      <c r="B576" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C576" s="3">
@@ -13873,7 +13876,7 @@
       <c r="A577" s="1">
         <v>60</v>
       </c>
-      <c r="B577" s="4" t="s">
+      <c r="B577" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C577" s="3">
@@ -13894,7 +13897,7 @@
       <c r="A578" s="1">
         <v>61</v>
       </c>
-      <c r="B578" s="4" t="s">
+      <c r="B578" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C578" s="3">
@@ -13915,7 +13918,7 @@
       <c r="A579" s="1">
         <v>61</v>
       </c>
-      <c r="B579" s="4" t="s">
+      <c r="B579" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C579" s="3">
@@ -13936,7 +13939,7 @@
       <c r="A580" s="1">
         <v>62</v>
       </c>
-      <c r="B580" s="4" t="s">
+      <c r="B580" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C580" s="3">
@@ -13957,7 +13960,7 @@
       <c r="A581" s="1">
         <v>62</v>
       </c>
-      <c r="B581" s="4" t="s">
+      <c r="B581" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C581" s="3">
@@ -13978,7 +13981,7 @@
       <c r="A582" s="1">
         <v>63</v>
       </c>
-      <c r="B582" s="4" t="s">
+      <c r="B582" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C582" s="3">
@@ -13999,7 +14002,7 @@
       <c r="A583" s="1">
         <v>63</v>
       </c>
-      <c r="B583" s="4" t="s">
+      <c r="B583" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C583" s="3">
@@ -14020,7 +14023,7 @@
       <c r="A584" s="1">
         <v>64</v>
       </c>
-      <c r="B584" s="4" t="s">
+      <c r="B584" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C584" s="3">
@@ -14041,7 +14044,7 @@
       <c r="A585" s="1">
         <v>64</v>
       </c>
-      <c r="B585" s="4" t="s">
+      <c r="B585" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C585" s="3">
@@ -14062,7 +14065,7 @@
       <c r="A586" s="1">
         <v>65</v>
       </c>
-      <c r="B586" s="4" t="s">
+      <c r="B586" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C586" s="3">
@@ -14083,7 +14086,7 @@
       <c r="A587" s="1">
         <v>65</v>
       </c>
-      <c r="B587" s="4" t="s">
+      <c r="B587" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C587" s="3">
@@ -14104,7 +14107,7 @@
       <c r="A588" s="1">
         <v>66</v>
       </c>
-      <c r="B588" s="4" t="s">
+      <c r="B588" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C588" s="3">
@@ -14125,7 +14128,7 @@
       <c r="A589" s="1">
         <v>66</v>
       </c>
-      <c r="B589" s="4" t="s">
+      <c r="B589" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C589" s="3">
@@ -14146,7 +14149,7 @@
       <c r="A590" s="1">
         <v>67</v>
       </c>
-      <c r="B590" s="4" t="s">
+      <c r="B590" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C590" s="3">
@@ -14167,7 +14170,7 @@
       <c r="A591" s="1">
         <v>67</v>
       </c>
-      <c r="B591" s="4" t="s">
+      <c r="B591" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C591" s="3">
@@ -14188,7 +14191,7 @@
       <c r="A592" s="1">
         <v>67</v>
       </c>
-      <c r="B592" s="4" t="s">
+      <c r="B592" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C592" s="3">
@@ -14209,7 +14212,7 @@
       <c r="A593" s="1">
         <v>68</v>
       </c>
-      <c r="B593" s="4" t="s">
+      <c r="B593" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C593" s="3">
@@ -14230,7 +14233,7 @@
       <c r="A594" s="1">
         <v>68</v>
       </c>
-      <c r="B594" s="4" t="s">
+      <c r="B594" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C594" s="3">
@@ -14251,7 +14254,7 @@
       <c r="A595" s="1">
         <v>68</v>
       </c>
-      <c r="B595" s="4" t="s">
+      <c r="B595" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C595" s="3">
@@ -14272,7 +14275,7 @@
       <c r="A596" s="1">
         <v>69</v>
       </c>
-      <c r="B596" s="4" t="s">
+      <c r="B596" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C596" s="3">
@@ -14293,7 +14296,7 @@
       <c r="A597" s="1">
         <v>69</v>
       </c>
-      <c r="B597" s="4" t="s">
+      <c r="B597" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C597" s="3">
@@ -14314,7 +14317,7 @@
       <c r="A598" s="1">
         <v>69</v>
       </c>
-      <c r="B598" s="4" t="s">
+      <c r="B598" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C598" s="3">
@@ -14335,7 +14338,7 @@
       <c r="A599" s="1">
         <v>70</v>
       </c>
-      <c r="B599" s="4" t="s">
+      <c r="B599" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C599" s="3">
@@ -14356,7 +14359,7 @@
       <c r="A600" s="1">
         <v>70</v>
       </c>
-      <c r="B600" s="4" t="s">
+      <c r="B600" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C600" s="3">
@@ -14377,7 +14380,7 @@
       <c r="A601" s="1">
         <v>70</v>
       </c>
-      <c r="B601" s="4" t="s">
+      <c r="B601" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C601" s="3">
@@ -14398,7 +14401,7 @@
       <c r="A602" s="1">
         <v>71</v>
       </c>
-      <c r="B602" s="4" t="s">
+      <c r="B602" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C602" s="3">
@@ -14419,7 +14422,7 @@
       <c r="A603" s="1">
         <v>71</v>
       </c>
-      <c r="B603" s="4" t="s">
+      <c r="B603" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C603" s="3">
@@ -14440,7 +14443,7 @@
       <c r="A604" s="1">
         <v>72</v>
       </c>
-      <c r="B604" s="4" t="s">
+      <c r="B604" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C604" s="3">
@@ -14461,7 +14464,7 @@
       <c r="A605" s="1">
         <v>72</v>
       </c>
-      <c r="B605" s="4" t="s">
+      <c r="B605" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C605" s="3">
@@ -14482,7 +14485,7 @@
       <c r="A606" s="1">
         <v>73</v>
       </c>
-      <c r="B606" s="4" t="s">
+      <c r="B606" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C606" s="3">
@@ -14503,7 +14506,7 @@
       <c r="A607" s="1">
         <v>73</v>
       </c>
-      <c r="B607" s="4" t="s">
+      <c r="B607" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C607" s="3">
@@ -14524,7 +14527,7 @@
       <c r="A608" s="1">
         <v>74</v>
       </c>
-      <c r="B608" s="4" t="s">
+      <c r="B608" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C608" s="3">
@@ -14545,7 +14548,7 @@
       <c r="A609" s="1">
         <v>74</v>
       </c>
-      <c r="B609" s="4" t="s">
+      <c r="B609" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C609" s="3">
@@ -14566,7 +14569,7 @@
       <c r="A610" s="1">
         <v>74</v>
       </c>
-      <c r="B610" s="4" t="s">
+      <c r="B610" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C610" s="3">
@@ -14587,7 +14590,7 @@
       <c r="A611" s="1">
         <v>75</v>
       </c>
-      <c r="B611" s="4" t="s">
+      <c r="B611" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C611" s="3">
@@ -14608,7 +14611,7 @@
       <c r="A612" s="1">
         <v>75</v>
       </c>
-      <c r="B612" s="4" t="s">
+      <c r="B612" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C612" s="3">
@@ -14629,7 +14632,7 @@
       <c r="A613" s="1">
         <v>76</v>
       </c>
-      <c r="B613" s="4" t="s">
+      <c r="B613" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C613" s="3">
@@ -14650,7 +14653,7 @@
       <c r="A614" s="1">
         <v>76</v>
       </c>
-      <c r="B614" s="4" t="s">
+      <c r="B614" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C614" s="3">
@@ -14671,7 +14674,7 @@
       <c r="A615" s="1">
         <v>76</v>
       </c>
-      <c r="B615" s="4" t="s">
+      <c r="B615" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C615" s="3">
@@ -14692,7 +14695,7 @@
       <c r="A616" s="1">
         <v>77</v>
       </c>
-      <c r="B616" s="4" t="s">
+      <c r="B616" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C616" s="3">
@@ -14713,7 +14716,7 @@
       <c r="A617" s="1">
         <v>77</v>
       </c>
-      <c r="B617" s="4" t="s">
+      <c r="B617" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C617" s="3">
@@ -14734,7 +14737,7 @@
       <c r="A618" s="1">
         <v>78</v>
       </c>
-      <c r="B618" s="4" t="s">
+      <c r="B618" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C618" s="3">
@@ -14755,7 +14758,7 @@
       <c r="A619" s="1">
         <v>78</v>
       </c>
-      <c r="B619" s="4" t="s">
+      <c r="B619" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C619" s="3">
@@ -14776,7 +14779,7 @@
       <c r="A620" s="1">
         <v>79</v>
       </c>
-      <c r="B620" s="4" t="s">
+      <c r="B620" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C620" s="3">
@@ -14797,7 +14800,7 @@
       <c r="A621" s="1">
         <v>79</v>
       </c>
-      <c r="B621" s="4" t="s">
+      <c r="B621" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C621" s="3">
@@ -14818,7 +14821,7 @@
       <c r="A622" s="1">
         <v>80</v>
       </c>
-      <c r="B622" s="4" t="s">
+      <c r="B622" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C622" s="3">
@@ -14839,7 +14842,7 @@
       <c r="A623" s="1">
         <v>81</v>
       </c>
-      <c r="B623" s="4" t="s">
+      <c r="B623" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C623" s="3">
@@ -14860,7 +14863,7 @@
       <c r="A624" s="1">
         <v>82</v>
       </c>
-      <c r="B624" s="4" t="s">
+      <c r="B624" s="5" t="s">
         <v>87</v>
       </c>
       <c r="C624" s="3">
@@ -14881,7 +14884,7 @@
       <c r="A625" s="1">
         <v>83</v>
       </c>
-      <c r="B625" s="4" t="s">
+      <c r="B625" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C625" s="3">
@@ -14902,7 +14905,7 @@
       <c r="A626" s="1">
         <v>83</v>
       </c>
-      <c r="B626" s="4" t="s">
+      <c r="B626" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C626" s="3">
@@ -14923,7 +14926,7 @@
       <c r="A627" s="1">
         <v>83</v>
       </c>
-      <c r="B627" s="4" t="s">
+      <c r="B627" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C627" s="3">
@@ -14944,7 +14947,7 @@
       <c r="A628" s="1">
         <v>84</v>
       </c>
-      <c r="B628" s="4" t="s">
+      <c r="B628" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C628" s="3">
@@ -14965,7 +14968,7 @@
       <c r="A629" s="1">
         <v>84</v>
       </c>
-      <c r="B629" s="4" t="s">
+      <c r="B629" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C629" s="3">
@@ -14985,7 +14988,7 @@
       <c r="A630" s="1">
         <v>85</v>
       </c>
-      <c r="B630" s="4" t="s">
+      <c r="B630" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C630" s="3">
@@ -15006,7 +15009,7 @@
       <c r="A631" s="1">
         <v>86</v>
       </c>
-      <c r="B631" s="4" t="s">
+      <c r="B631" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C631" s="3">
@@ -15027,7 +15030,7 @@
       <c r="A632" s="1">
         <v>87</v>
       </c>
-      <c r="B632" s="4" t="s">
+      <c r="B632" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C632" s="3">
@@ -15048,7 +15051,7 @@
       <c r="A633" s="1">
         <v>87</v>
       </c>
-      <c r="B633" s="4" t="s">
+      <c r="B633" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C633" s="3">
@@ -15069,7 +15072,7 @@
       <c r="A634" s="1">
         <v>88</v>
       </c>
-      <c r="B634" s="4" t="s">
+      <c r="B634" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C634" s="3">
@@ -15090,7 +15093,7 @@
       <c r="A635" s="1">
         <v>89</v>
       </c>
-      <c r="B635" s="4" t="s">
+      <c r="B635" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C635" s="3">
@@ -15111,7 +15114,7 @@
       <c r="A636" s="1">
         <v>89</v>
       </c>
-      <c r="B636" s="4" t="s">
+      <c r="B636" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C636" s="3">
@@ -15132,7 +15135,7 @@
       <c r="A637" s="1">
         <v>90</v>
       </c>
-      <c r="B637" s="4" t="s">
+      <c r="B637" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C637" s="3">
@@ -15153,7 +15156,7 @@
       <c r="A638" s="1">
         <v>91</v>
       </c>
-      <c r="B638" s="4" t="s">
+      <c r="B638" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C638" s="3">
@@ -15174,7 +15177,7 @@
       <c r="A639" s="1">
         <v>92</v>
       </c>
-      <c r="B639" s="4" t="s">
+      <c r="B639" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C639" s="3">
@@ -15195,7 +15198,7 @@
       <c r="A640" s="1">
         <v>92</v>
       </c>
-      <c r="B640" s="4" t="s">
+      <c r="B640" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C640" s="3">
@@ -15216,7 +15219,7 @@
       <c r="A641" s="1">
         <v>93</v>
       </c>
-      <c r="B641" s="4" t="s">
+      <c r="B641" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C641" s="3">
@@ -15237,7 +15240,7 @@
       <c r="A642" s="1">
         <v>94</v>
       </c>
-      <c r="B642" s="4" t="s">
+      <c r="B642" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C642" s="3">
@@ -15258,7 +15261,7 @@
       <c r="A643" s="1">
         <v>95</v>
       </c>
-      <c r="B643" s="4" t="s">
+      <c r="B643" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C643" s="3">
@@ -15279,7 +15282,7 @@
       <c r="A644" s="1">
         <v>96</v>
       </c>
-      <c r="B644" s="4" t="s">
+      <c r="B644" s="5" t="s">
         <v>101</v>
       </c>
       <c r="C644" s="3">
@@ -15300,7 +15303,7 @@
       <c r="A645" s="1">
         <v>97</v>
       </c>
-      <c r="B645" s="4" t="s">
+      <c r="B645" s="5" t="s">
         <v>102</v>
       </c>
       <c r="C645" s="3">
@@ -15321,7 +15324,7 @@
       <c r="A646" s="1">
         <v>98</v>
       </c>
-      <c r="B646" s="4" t="s">
+      <c r="B646" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C646" s="3">
@@ -15342,7 +15345,7 @@
       <c r="A647" s="1">
         <v>98</v>
       </c>
-      <c r="B647" s="4" t="s">
+      <c r="B647" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C647" s="3">
@@ -15363,7 +15366,7 @@
       <c r="A648" s="1">
         <v>99</v>
       </c>
-      <c r="B648" s="4" t="s">
+      <c r="B648" s="5" t="s">
         <v>104</v>
       </c>
       <c r="C648" s="3">
@@ -15384,7 +15387,7 @@
       <c r="A649" s="1">
         <v>100</v>
       </c>
-      <c r="B649" s="4" t="s">
+      <c r="B649" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C649" s="3">
@@ -15393,7 +15396,7 @@
       <c r="D649" s="3">
         <v>5</v>
       </c>
-      <c r="E649" s="5">
+      <c r="E649" s="6">
         <v>599</v>
       </c>
       <c r="F649" s="3">
@@ -15405,7 +15408,7 @@
       <c r="A650" s="1">
         <v>100</v>
       </c>
-      <c r="B650" s="4" t="s">
+      <c r="B650" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C650" s="3">
@@ -15426,7 +15429,7 @@
       <c r="A651" s="1">
         <v>101</v>
       </c>
-      <c r="B651" s="4" t="s">
+      <c r="B651" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C651" s="3">
@@ -15447,7 +15450,7 @@
       <c r="A652" s="1">
         <v>102</v>
       </c>
-      <c r="B652" s="4" t="s">
+      <c r="B652" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C652" s="3">
@@ -15468,7 +15471,7 @@
       <c r="A653" s="1">
         <v>103</v>
       </c>
-      <c r="B653" s="4" t="s">
+      <c r="B653" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C653" s="3">
@@ -15489,7 +15492,7 @@
       <c r="A654" s="1">
         <v>104</v>
       </c>
-      <c r="B654" s="4" t="s">
+      <c r="B654" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C654" s="3">
@@ -15510,7 +15513,7 @@
       <c r="A655" s="1">
         <v>105</v>
       </c>
-      <c r="B655" s="4" t="s">
+      <c r="B655" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C655" s="3">
@@ -15531,7 +15534,7 @@
       <c r="A656" s="1">
         <v>106</v>
       </c>
-      <c r="B656" s="4" t="s">
+      <c r="B656" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C656" s="3">
@@ -15552,7 +15555,7 @@
       <c r="A657" s="1">
         <v>107</v>
       </c>
-      <c r="B657" s="4" t="s">
+      <c r="B657" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C657" s="3">
@@ -15573,7 +15576,7 @@
       <c r="A658" s="1">
         <v>108</v>
       </c>
-      <c r="B658" s="4" t="s">
+      <c r="B658" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C658" s="3">
@@ -15594,7 +15597,7 @@
       <c r="A659" s="1">
         <v>109</v>
       </c>
-      <c r="B659" s="4" t="s">
+      <c r="B659" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C659" s="3">
@@ -15615,7 +15618,7 @@
       <c r="A660" s="1">
         <v>110</v>
       </c>
-      <c r="B660" s="4" t="s">
+      <c r="B660" s="5" t="s">
         <v>115</v>
       </c>
       <c r="C660" s="3">
@@ -15636,7 +15639,7 @@
       <c r="A661" s="1">
         <v>111</v>
       </c>
-      <c r="B661" s="4" t="s">
+      <c r="B661" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C661" s="3">
@@ -15657,7 +15660,7 @@
       <c r="A662" s="1">
         <v>112</v>
       </c>
-      <c r="B662" s="4" t="s">
+      <c r="B662" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C662" s="3">
@@ -15678,7 +15681,7 @@
       <c r="A663" s="1">
         <v>113</v>
       </c>
-      <c r="B663" s="4" t="s">
+      <c r="B663" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C663" s="3">
@@ -15699,7 +15702,7 @@
       <c r="A664" s="1">
         <v>114</v>
       </c>
-      <c r="B664" s="4" t="s">
+      <c r="B664" s="5" t="s">
         <v>119</v>
       </c>
       <c r="C664" s="3">
@@ -18247,8 +18250,8 @@
       <c r="A121" s="3">
         <v>120</v>
       </c>
-      <c r="B121" s="1">
-        <v>6</v>
+      <c r="B121" s="4">
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -18271,8 +18274,8 @@
       <c r="A124" s="3">
         <v>123</v>
       </c>
-      <c r="B124" s="1">
-        <v>6</v>
+      <c r="B124" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -18440,7 +18443,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -18448,7 +18451,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:2">
